--- a/conf_fiscais.xlsx
+++ b/conf_fiscais.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Faturamento\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Faturamento\Desktop\nfe_sistema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9ED422-5F95-4DC9-BD5C-5BEA7FC5E479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0B2D24-34F2-4268-9DE9-C9824DB3C01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F76E099-F64F-4C5B-B230-95152170BA2F}"/>
   </bookViews>
@@ -17,11 +17,10 @@
     <sheet name="Config ST" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Config Fiscal'!$A$1:$T$105</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Config ST'!$A$1:$F$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Config Fiscal'!$A$1:$T$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Config ST'!$A$1:$F$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="31">
   <si>
     <t>ncm</t>
   </si>
@@ -510,7 +509,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
-  <dimension ref="A1:T105"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:T107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -657,7 +657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>84502090</v>
       </c>
@@ -719,7 +719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>84501900</v>
       </c>
@@ -781,7 +781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>73211100</v>
       </c>
@@ -843,7 +843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>94016100</v>
       </c>
@@ -905,7 +905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>94016100</v>
       </c>
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>94016100</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>94016100</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>94016100</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>94016100</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>84502020</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>84146000</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>84145990</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>84145990</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>84145990</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>84145990</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>84145990</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>84145110</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>84145110</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>84145110</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>94034000</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>94035000</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>94036000</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>73211100</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>84146000</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>84501900</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>84502020</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>84502090</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>94034000</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>94035000</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>94036000</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>94044000</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>94044000</v>
       </c>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>94044000</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>94044000</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>94044000</v>
       </c>
@@ -2889,7 +2889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>94044000</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>94044000</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>94044000</v>
       </c>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>94032010</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>94032010</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>94032010</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>94032010</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>94032010</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>94032010</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>94049000</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>94049000</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>94049000</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>94049000</v>
       </c>
@@ -3695,7 +3695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>94049000</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>94049000</v>
       </c>
@@ -3819,7 +3819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>85167910</v>
       </c>
@@ -3881,7 +3881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>85167920</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>85094010</v>
       </c>
@@ -4005,7 +4005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>85094050</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>85167910</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>85167920</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>85094010</v>
       </c>
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>85094050</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>85167910</v>
       </c>
@@ -4377,7 +4377,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>85167920</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>85094010</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>85094050</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>85167910</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>85167920</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>85094010</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>85094050</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>85167910</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>85167920</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>85094010</v>
       </c>
@@ -4997,7 +4997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>85094050</v>
       </c>
@@ -5059,7 +5059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>85167910</v>
       </c>
@@ -5121,7 +5121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>85167920</v>
       </c>
@@ -5183,7 +5183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>85094010</v>
       </c>
@@ -5245,7 +5245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>85094050</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>85167910</v>
       </c>
@@ -5369,7 +5369,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>85167920</v>
       </c>
@@ -5431,7 +5431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>85094010</v>
       </c>
@@ -5493,7 +5493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>85094050</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>85167910</v>
       </c>
@@ -5617,7 +5617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>85167920</v>
       </c>
@@ -5679,7 +5679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>85094010</v>
       </c>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>85094050</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>84186931</v>
       </c>
@@ -5865,7 +5865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>84186931</v>
       </c>
@@ -5927,7 +5927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>84186931</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>84186931</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>84186931</v>
       </c>
@@ -6113,7 +6113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>84186931</v>
       </c>
@@ -6175,7 +6175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>84186931</v>
       </c>
@@ -6237,7 +6237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>84186931</v>
       </c>
@@ -6299,7 +6299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>84145190</v>
       </c>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>84145190</v>
       </c>
@@ -6423,7 +6423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>84145190</v>
       </c>
@@ -6485,7 +6485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>84145190</v>
       </c>
@@ -6547,7 +6547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>84145190</v>
       </c>
@@ -6609,7 +6609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>84145190</v>
       </c>
@@ -6671,7 +6671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>84145190</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>84145190</v>
       </c>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>84145190</v>
       </c>
@@ -6857,7 +6857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>84145190</v>
       </c>
@@ -6919,7 +6919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>84145190</v>
       </c>
@@ -6981,7 +6981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>84145190</v>
       </c>
@@ -7043,8 +7043,138 @@
         <v>0</v>
       </c>
     </row>
+    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>73211100</v>
+      </c>
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106" t="s">
+        <v>20</v>
+      </c>
+      <c r="D106" t="s">
+        <v>21</v>
+      </c>
+      <c r="E106">
+        <v>6108</v>
+      </c>
+      <c r="F106">
+        <v>6102</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>3</v>
+      </c>
+      <c r="J106">
+        <v>12</v>
+      </c>
+      <c r="K106">
+        <v>53</v>
+      </c>
+      <c r="L106">
+        <v>999</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>1</v>
+      </c>
+      <c r="O106">
+        <v>1</v>
+      </c>
+      <c r="P106">
+        <v>1.65</v>
+      </c>
+      <c r="Q106">
+        <v>1</v>
+      </c>
+      <c r="R106">
+        <v>7.6</v>
+      </c>
+      <c r="S106">
+        <v>0</v>
+      </c>
+      <c r="T106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>84211210</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+      <c r="C107" t="s">
+        <v>20</v>
+      </c>
+      <c r="D107" t="s">
+        <v>21</v>
+      </c>
+      <c r="E107">
+        <v>6108</v>
+      </c>
+      <c r="F107">
+        <v>6102</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>3</v>
+      </c>
+      <c r="J107">
+        <v>12</v>
+      </c>
+      <c r="K107">
+        <v>53</v>
+      </c>
+      <c r="L107">
+        <v>999</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>1</v>
+      </c>
+      <c r="O107">
+        <v>1</v>
+      </c>
+      <c r="P107">
+        <v>1.65</v>
+      </c>
+      <c r="Q107">
+        <v>1</v>
+      </c>
+      <c r="R107">
+        <v>7.6</v>
+      </c>
+      <c r="S107">
+        <v>0</v>
+      </c>
+      <c r="T107">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T105" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}"/>
+  <autoFilter ref="A1:T106" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="84211210"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -7053,7 +7183,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27418B64-EF4D-4086-9A4A-8537F5F99C12}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -7184,7 +7314,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>84211210</v>
       </c>
@@ -7204,7 +7334,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>84211210</v>
       </c>
@@ -7484,7 +7614,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>84145190</v>
       </c>
@@ -7504,7 +7634,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>84145190</v>
       </c>
@@ -7524,7 +7654,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>84145190</v>
       </c>
@@ -7544,11 +7674,51 @@
         <v>12</v>
       </c>
     </row>
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>73211100</v>
+      </c>
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25">
+        <v>56.68</v>
+      </c>
+      <c r="E25">
+        <v>18</v>
+      </c>
+      <c r="F25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>84211210</v>
+      </c>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26">
+        <v>49.17</v>
+      </c>
+      <c r="E26">
+        <v>18</v>
+      </c>
+      <c r="F26">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F24" xr:uid="{27418B64-EF4D-4086-9A4A-8537F5F99C12}">
+  <autoFilter ref="A1:F25" xr:uid="{27418B64-EF4D-4086-9A4A-8537F5F99C12}">
     <filterColumn colId="0">
       <filters>
-        <filter val="84145190"/>
+        <filter val="84211210"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/conf_fiscais.xlsx
+++ b/conf_fiscais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Faturamento\Desktop\nfe_sistema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0B2D24-34F2-4268-9DE9-C9824DB3C01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B43D26-AB35-4602-AA1D-4E99A6EA93F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F76E099-F64F-4C5B-B230-95152170BA2F}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Config ST" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Config Fiscal'!$A$1:$T$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Config Fiscal'!$A$1:$T$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Config ST'!$A$1:$F$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="31">
   <si>
     <t>ncm</t>
   </si>
@@ -510,7 +510,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:T107"/>
+  <dimension ref="A1:T123"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -595,7 +595,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>84211210</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>84211210</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>94044000</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>3</v>
       </c>
       <c r="J34">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K34">
         <v>53</v>
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>94044000</v>
       </c>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>94044000</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>94044000</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>94044000</v>
       </c>
@@ -2889,7 +2889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>94044000</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>94044000</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>94044000</v>
       </c>
@@ -7105,7 +7105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>84211210</v>
       </c>
@@ -7167,11 +7167,1003 @@
         <v>0</v>
       </c>
     </row>
+    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>94042900</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+      <c r="C108" t="s">
+        <v>20</v>
+      </c>
+      <c r="D108" t="s">
+        <v>20</v>
+      </c>
+      <c r="E108">
+        <v>5102</v>
+      </c>
+      <c r="F108">
+        <v>5102</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>3</v>
+      </c>
+      <c r="J108">
+        <v>12</v>
+      </c>
+      <c r="K108">
+        <v>53</v>
+      </c>
+      <c r="L108">
+        <v>999</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>1</v>
+      </c>
+      <c r="O108">
+        <v>1</v>
+      </c>
+      <c r="P108">
+        <v>1.65</v>
+      </c>
+      <c r="Q108">
+        <v>1</v>
+      </c>
+      <c r="R108">
+        <v>7.6</v>
+      </c>
+      <c r="S108">
+        <v>0</v>
+      </c>
+      <c r="T108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>94042900</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+      <c r="C109" t="s">
+        <v>20</v>
+      </c>
+      <c r="D109" t="s">
+        <v>22</v>
+      </c>
+      <c r="E109">
+        <v>6108</v>
+      </c>
+      <c r="F109">
+        <v>6102</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>3</v>
+      </c>
+      <c r="J109">
+        <v>12</v>
+      </c>
+      <c r="K109">
+        <v>53</v>
+      </c>
+      <c r="L109">
+        <v>999</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>1</v>
+      </c>
+      <c r="O109">
+        <v>1</v>
+      </c>
+      <c r="P109">
+        <v>1.65</v>
+      </c>
+      <c r="Q109">
+        <v>1</v>
+      </c>
+      <c r="R109">
+        <v>7.6</v>
+      </c>
+      <c r="S109">
+        <v>0</v>
+      </c>
+      <c r="T109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>94042900</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+      <c r="C110" t="s">
+        <v>20</v>
+      </c>
+      <c r="D110" t="s">
+        <v>23</v>
+      </c>
+      <c r="E110">
+        <v>6108</v>
+      </c>
+      <c r="F110">
+        <v>6102</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>3</v>
+      </c>
+      <c r="J110">
+        <v>12</v>
+      </c>
+      <c r="K110">
+        <v>53</v>
+      </c>
+      <c r="L110">
+        <v>999</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>1</v>
+      </c>
+      <c r="O110">
+        <v>1</v>
+      </c>
+      <c r="P110">
+        <v>1.65</v>
+      </c>
+      <c r="Q110">
+        <v>1</v>
+      </c>
+      <c r="R110">
+        <v>7.6</v>
+      </c>
+      <c r="S110">
+        <v>0</v>
+      </c>
+      <c r="T110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>94042900</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+      <c r="C111" t="s">
+        <v>20</v>
+      </c>
+      <c r="D111" t="s">
+        <v>21</v>
+      </c>
+      <c r="E111">
+        <v>6108</v>
+      </c>
+      <c r="F111">
+        <v>6102</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>3</v>
+      </c>
+      <c r="J111">
+        <v>12</v>
+      </c>
+      <c r="K111">
+        <v>53</v>
+      </c>
+      <c r="L111">
+        <v>999</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>1</v>
+      </c>
+      <c r="O111">
+        <v>1</v>
+      </c>
+      <c r="P111">
+        <v>1.65</v>
+      </c>
+      <c r="Q111">
+        <v>1</v>
+      </c>
+      <c r="R111">
+        <v>7.6</v>
+      </c>
+      <c r="S111">
+        <v>0</v>
+      </c>
+      <c r="T111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>94042900</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+      <c r="C112" t="s">
+        <v>21</v>
+      </c>
+      <c r="D112" t="s">
+        <v>20</v>
+      </c>
+      <c r="E112">
+        <v>6108</v>
+      </c>
+      <c r="F112">
+        <v>6102</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>3</v>
+      </c>
+      <c r="J112">
+        <v>12</v>
+      </c>
+      <c r="K112">
+        <v>53</v>
+      </c>
+      <c r="L112">
+        <v>999</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>1</v>
+      </c>
+      <c r="O112">
+        <v>1</v>
+      </c>
+      <c r="P112">
+        <v>1.65</v>
+      </c>
+      <c r="Q112">
+        <v>1</v>
+      </c>
+      <c r="R112">
+        <v>7.6</v>
+      </c>
+      <c r="S112">
+        <v>0</v>
+      </c>
+      <c r="T112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>94042900</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+      <c r="C113" t="s">
+        <v>21</v>
+      </c>
+      <c r="D113" t="s">
+        <v>22</v>
+      </c>
+      <c r="E113">
+        <v>6108</v>
+      </c>
+      <c r="F113">
+        <v>6102</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <v>3</v>
+      </c>
+      <c r="J113">
+        <v>12</v>
+      </c>
+      <c r="K113">
+        <v>53</v>
+      </c>
+      <c r="L113">
+        <v>999</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>1</v>
+      </c>
+      <c r="O113">
+        <v>1</v>
+      </c>
+      <c r="P113">
+        <v>1.65</v>
+      </c>
+      <c r="Q113">
+        <v>1</v>
+      </c>
+      <c r="R113">
+        <v>7.6</v>
+      </c>
+      <c r="S113">
+        <v>0</v>
+      </c>
+      <c r="T113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>94042900</v>
+      </c>
+      <c r="B114">
+        <v>0</v>
+      </c>
+      <c r="C114" t="s">
+        <v>21</v>
+      </c>
+      <c r="D114" t="s">
+        <v>23</v>
+      </c>
+      <c r="E114">
+        <v>6108</v>
+      </c>
+      <c r="F114">
+        <v>6102</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <v>3</v>
+      </c>
+      <c r="J114">
+        <v>12</v>
+      </c>
+      <c r="K114">
+        <v>53</v>
+      </c>
+      <c r="L114">
+        <v>999</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>1</v>
+      </c>
+      <c r="O114">
+        <v>1</v>
+      </c>
+      <c r="P114">
+        <v>1.65</v>
+      </c>
+      <c r="Q114">
+        <v>1</v>
+      </c>
+      <c r="R114">
+        <v>7.6</v>
+      </c>
+      <c r="S114">
+        <v>0</v>
+      </c>
+      <c r="T114">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>94042900</v>
+      </c>
+      <c r="B115">
+        <v>0</v>
+      </c>
+      <c r="C115" t="s">
+        <v>21</v>
+      </c>
+      <c r="D115" t="s">
+        <v>21</v>
+      </c>
+      <c r="E115">
+        <v>5102</v>
+      </c>
+      <c r="F115">
+        <v>5102</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>3</v>
+      </c>
+      <c r="J115">
+        <v>17</v>
+      </c>
+      <c r="K115">
+        <v>53</v>
+      </c>
+      <c r="L115">
+        <v>999</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>1</v>
+      </c>
+      <c r="O115">
+        <v>1</v>
+      </c>
+      <c r="P115">
+        <v>1.65</v>
+      </c>
+      <c r="Q115">
+        <v>1</v>
+      </c>
+      <c r="R115">
+        <v>7.6</v>
+      </c>
+      <c r="S115">
+        <v>0</v>
+      </c>
+      <c r="T115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>94041000</v>
+      </c>
+      <c r="B116">
+        <v>0</v>
+      </c>
+      <c r="C116" t="s">
+        <v>20</v>
+      </c>
+      <c r="D116" t="s">
+        <v>20</v>
+      </c>
+      <c r="E116">
+        <v>5102</v>
+      </c>
+      <c r="F116">
+        <v>5102</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>3</v>
+      </c>
+      <c r="J116">
+        <v>12</v>
+      </c>
+      <c r="K116">
+        <v>53</v>
+      </c>
+      <c r="L116">
+        <v>999</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>1</v>
+      </c>
+      <c r="O116">
+        <v>1</v>
+      </c>
+      <c r="P116">
+        <v>1.65</v>
+      </c>
+      <c r="Q116">
+        <v>1</v>
+      </c>
+      <c r="R116">
+        <v>7.6</v>
+      </c>
+      <c r="S116">
+        <v>0</v>
+      </c>
+      <c r="T116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>94041000</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+      <c r="C117" t="s">
+        <v>20</v>
+      </c>
+      <c r="D117" t="s">
+        <v>22</v>
+      </c>
+      <c r="E117">
+        <v>6108</v>
+      </c>
+      <c r="F117">
+        <v>6102</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>3</v>
+      </c>
+      <c r="J117">
+        <v>12</v>
+      </c>
+      <c r="K117">
+        <v>53</v>
+      </c>
+      <c r="L117">
+        <v>999</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>1</v>
+      </c>
+      <c r="O117">
+        <v>1</v>
+      </c>
+      <c r="P117">
+        <v>1.65</v>
+      </c>
+      <c r="Q117">
+        <v>1</v>
+      </c>
+      <c r="R117">
+        <v>7.6</v>
+      </c>
+      <c r="S117">
+        <v>0</v>
+      </c>
+      <c r="T117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>94041000</v>
+      </c>
+      <c r="B118">
+        <v>0</v>
+      </c>
+      <c r="C118" t="s">
+        <v>20</v>
+      </c>
+      <c r="D118" t="s">
+        <v>23</v>
+      </c>
+      <c r="E118">
+        <v>6108</v>
+      </c>
+      <c r="F118">
+        <v>6102</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>3</v>
+      </c>
+      <c r="J118">
+        <v>12</v>
+      </c>
+      <c r="K118">
+        <v>53</v>
+      </c>
+      <c r="L118">
+        <v>999</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>1</v>
+      </c>
+      <c r="O118">
+        <v>1</v>
+      </c>
+      <c r="P118">
+        <v>1.65</v>
+      </c>
+      <c r="Q118">
+        <v>1</v>
+      </c>
+      <c r="R118">
+        <v>7.6</v>
+      </c>
+      <c r="S118">
+        <v>0</v>
+      </c>
+      <c r="T118">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>94041000</v>
+      </c>
+      <c r="B119">
+        <v>0</v>
+      </c>
+      <c r="C119" t="s">
+        <v>20</v>
+      </c>
+      <c r="D119" t="s">
+        <v>21</v>
+      </c>
+      <c r="E119">
+        <v>6108</v>
+      </c>
+      <c r="F119">
+        <v>6102</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>3</v>
+      </c>
+      <c r="J119">
+        <v>12</v>
+      </c>
+      <c r="K119">
+        <v>53</v>
+      </c>
+      <c r="L119">
+        <v>999</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>1</v>
+      </c>
+      <c r="O119">
+        <v>1</v>
+      </c>
+      <c r="P119">
+        <v>1.65</v>
+      </c>
+      <c r="Q119">
+        <v>1</v>
+      </c>
+      <c r="R119">
+        <v>7.6</v>
+      </c>
+      <c r="S119">
+        <v>0</v>
+      </c>
+      <c r="T119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>94041000</v>
+      </c>
+      <c r="B120">
+        <v>0</v>
+      </c>
+      <c r="C120" t="s">
+        <v>21</v>
+      </c>
+      <c r="D120" t="s">
+        <v>20</v>
+      </c>
+      <c r="E120">
+        <v>6108</v>
+      </c>
+      <c r="F120">
+        <v>6102</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>3</v>
+      </c>
+      <c r="J120">
+        <v>12</v>
+      </c>
+      <c r="K120">
+        <v>53</v>
+      </c>
+      <c r="L120">
+        <v>999</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>1</v>
+      </c>
+      <c r="O120">
+        <v>1</v>
+      </c>
+      <c r="P120">
+        <v>1.65</v>
+      </c>
+      <c r="Q120">
+        <v>1</v>
+      </c>
+      <c r="R120">
+        <v>7.6</v>
+      </c>
+      <c r="S120">
+        <v>0</v>
+      </c>
+      <c r="T120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>94041000</v>
+      </c>
+      <c r="B121">
+        <v>0</v>
+      </c>
+      <c r="C121" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121" t="s">
+        <v>22</v>
+      </c>
+      <c r="E121">
+        <v>6108</v>
+      </c>
+      <c r="F121">
+        <v>6102</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <v>3</v>
+      </c>
+      <c r="J121">
+        <v>12</v>
+      </c>
+      <c r="K121">
+        <v>53</v>
+      </c>
+      <c r="L121">
+        <v>999</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>1</v>
+      </c>
+      <c r="O121">
+        <v>1</v>
+      </c>
+      <c r="P121">
+        <v>1.65</v>
+      </c>
+      <c r="Q121">
+        <v>1</v>
+      </c>
+      <c r="R121">
+        <v>7.6</v>
+      </c>
+      <c r="S121">
+        <v>0</v>
+      </c>
+      <c r="T121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>94041000</v>
+      </c>
+      <c r="B122">
+        <v>0</v>
+      </c>
+      <c r="C122" t="s">
+        <v>21</v>
+      </c>
+      <c r="D122" t="s">
+        <v>23</v>
+      </c>
+      <c r="E122">
+        <v>6108</v>
+      </c>
+      <c r="F122">
+        <v>6102</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>3</v>
+      </c>
+      <c r="J122">
+        <v>12</v>
+      </c>
+      <c r="K122">
+        <v>53</v>
+      </c>
+      <c r="L122">
+        <v>999</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>1</v>
+      </c>
+      <c r="O122">
+        <v>1</v>
+      </c>
+      <c r="P122">
+        <v>1.65</v>
+      </c>
+      <c r="Q122">
+        <v>1</v>
+      </c>
+      <c r="R122">
+        <v>7.6</v>
+      </c>
+      <c r="S122">
+        <v>0</v>
+      </c>
+      <c r="T122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>94041000</v>
+      </c>
+      <c r="B123">
+        <v>0</v>
+      </c>
+      <c r="C123" t="s">
+        <v>21</v>
+      </c>
+      <c r="D123" t="s">
+        <v>21</v>
+      </c>
+      <c r="E123">
+        <v>5102</v>
+      </c>
+      <c r="F123">
+        <v>5102</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>3</v>
+      </c>
+      <c r="J123">
+        <v>17</v>
+      </c>
+      <c r="K123">
+        <v>53</v>
+      </c>
+      <c r="L123">
+        <v>999</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>1</v>
+      </c>
+      <c r="O123">
+        <v>1</v>
+      </c>
+      <c r="P123">
+        <v>1.65</v>
+      </c>
+      <c r="Q123">
+        <v>1</v>
+      </c>
+      <c r="R123">
+        <v>7.6</v>
+      </c>
+      <c r="S123">
+        <v>0</v>
+      </c>
+      <c r="T123">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T106" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
+  <autoFilter ref="A1:T107" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
     <filterColumn colId="0">
       <filters>
-        <filter val="84211210"/>
+        <filter val="94044000"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/conf_fiscais.xlsx
+++ b/conf_fiscais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Faturamento\Desktop\nfe_sistema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B43D26-AB35-4602-AA1D-4E99A6EA93F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71878AF-EF25-4737-9B9E-6E3EA3E6D1CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F76E099-F64F-4C5B-B230-95152170BA2F}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Config ST" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Config Fiscal'!$A$1:$T$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Config Fiscal'!$A$1:$T$135</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Config ST'!$A$1:$F$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="31">
   <si>
     <t>ncm</t>
   </si>
@@ -510,7 +510,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:T123"/>
+  <dimension ref="A1:T141"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -518,9 +518,10 @@
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5546875" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
     <col min="9" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" customWidth="1"/>
     <col min="11" max="11" width="8.77734375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.109375" bestFit="1" customWidth="1"/>
@@ -528,7 +529,7 @@
     <col min="15" max="15" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.5546875" customWidth="1"/>
     <col min="19" max="19" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -1959,7 +1960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>94036000</v>
       </c>
@@ -2517,7 +2518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>94036000</v>
       </c>
@@ -2579,7 +2580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>94044000</v>
       </c>
@@ -2641,7 +2642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>94044000</v>
       </c>
@@ -2703,7 +2704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>94044000</v>
       </c>
@@ -2765,7 +2766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>94044000</v>
       </c>
@@ -2827,7 +2828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>94044000</v>
       </c>
@@ -2889,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>94044000</v>
       </c>
@@ -2951,7 +2952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>94044000</v>
       </c>
@@ -3013,7 +3014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>94044000</v>
       </c>
@@ -7167,7 +7168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>94042900</v>
       </c>
@@ -7229,7 +7230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>94042900</v>
       </c>
@@ -7291,7 +7292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>94042900</v>
       </c>
@@ -7353,7 +7354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>94042900</v>
       </c>
@@ -7415,7 +7416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>94042900</v>
       </c>
@@ -7477,7 +7478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>94042900</v>
       </c>
@@ -7539,7 +7540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>94042900</v>
       </c>
@@ -7601,7 +7602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>94042900</v>
       </c>
@@ -7663,7 +7664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>94041000</v>
       </c>
@@ -7725,7 +7726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>94041000</v>
       </c>
@@ -7787,7 +7788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>94041000</v>
       </c>
@@ -7849,7 +7850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>94041000</v>
       </c>
@@ -7911,7 +7912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>94041000</v>
       </c>
@@ -7973,7 +7974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>94041000</v>
       </c>
@@ -8035,7 +8036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>94041000</v>
       </c>
@@ -8097,7 +8098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>94041000</v>
       </c>
@@ -8159,11 +8160,1127 @@
         <v>0</v>
       </c>
     </row>
+    <row r="124" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>94035000</v>
+      </c>
+      <c r="B124">
+        <v>0</v>
+      </c>
+      <c r="C124" t="s">
+        <v>20</v>
+      </c>
+      <c r="D124" t="s">
+        <v>22</v>
+      </c>
+      <c r="E124">
+        <v>6108</v>
+      </c>
+      <c r="F124">
+        <v>6102</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>3</v>
+      </c>
+      <c r="J124">
+        <v>12</v>
+      </c>
+      <c r="K124">
+        <v>53</v>
+      </c>
+      <c r="L124">
+        <v>999</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>1</v>
+      </c>
+      <c r="O124">
+        <v>1</v>
+      </c>
+      <c r="P124">
+        <v>1.65</v>
+      </c>
+      <c r="Q124">
+        <v>1</v>
+      </c>
+      <c r="R124">
+        <v>7.6</v>
+      </c>
+      <c r="S124">
+        <v>0</v>
+      </c>
+      <c r="T124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>94035000</v>
+      </c>
+      <c r="B125">
+        <v>0</v>
+      </c>
+      <c r="C125" t="s">
+        <v>20</v>
+      </c>
+      <c r="D125" t="s">
+        <v>23</v>
+      </c>
+      <c r="E125">
+        <v>6108</v>
+      </c>
+      <c r="F125">
+        <v>6102</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>3</v>
+      </c>
+      <c r="J125">
+        <v>12</v>
+      </c>
+      <c r="K125">
+        <v>53</v>
+      </c>
+      <c r="L125">
+        <v>999</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>1</v>
+      </c>
+      <c r="O125">
+        <v>1</v>
+      </c>
+      <c r="P125">
+        <v>1.65</v>
+      </c>
+      <c r="Q125">
+        <v>1</v>
+      </c>
+      <c r="R125">
+        <v>7.6</v>
+      </c>
+      <c r="S125">
+        <v>0</v>
+      </c>
+      <c r="T125">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>94035000</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+      <c r="C126" t="s">
+        <v>20</v>
+      </c>
+      <c r="D126" t="s">
+        <v>21</v>
+      </c>
+      <c r="E126">
+        <v>6108</v>
+      </c>
+      <c r="F126">
+        <v>6102</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>3</v>
+      </c>
+      <c r="J126">
+        <v>12</v>
+      </c>
+      <c r="K126">
+        <v>53</v>
+      </c>
+      <c r="L126">
+        <v>999</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>1</v>
+      </c>
+      <c r="O126">
+        <v>1</v>
+      </c>
+      <c r="P126">
+        <v>1.65</v>
+      </c>
+      <c r="Q126">
+        <v>1</v>
+      </c>
+      <c r="R126">
+        <v>7.6</v>
+      </c>
+      <c r="S126">
+        <v>0</v>
+      </c>
+      <c r="T126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>94035000</v>
+      </c>
+      <c r="B127">
+        <v>0</v>
+      </c>
+      <c r="C127" t="s">
+        <v>21</v>
+      </c>
+      <c r="D127" t="s">
+        <v>22</v>
+      </c>
+      <c r="E127">
+        <v>6108</v>
+      </c>
+      <c r="F127">
+        <v>6102</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>3</v>
+      </c>
+      <c r="J127">
+        <v>12</v>
+      </c>
+      <c r="K127">
+        <v>53</v>
+      </c>
+      <c r="L127">
+        <v>999</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>1</v>
+      </c>
+      <c r="O127">
+        <v>1</v>
+      </c>
+      <c r="P127">
+        <v>1.65</v>
+      </c>
+      <c r="Q127">
+        <v>1</v>
+      </c>
+      <c r="R127">
+        <v>7.6</v>
+      </c>
+      <c r="S127">
+        <v>0</v>
+      </c>
+      <c r="T127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>94035000</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128" t="s">
+        <v>21</v>
+      </c>
+      <c r="D128" t="s">
+        <v>23</v>
+      </c>
+      <c r="E128">
+        <v>6108</v>
+      </c>
+      <c r="F128">
+        <v>6102</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>3</v>
+      </c>
+      <c r="J128">
+        <v>12</v>
+      </c>
+      <c r="K128">
+        <v>53</v>
+      </c>
+      <c r="L128">
+        <v>999</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>1</v>
+      </c>
+      <c r="O128">
+        <v>1</v>
+      </c>
+      <c r="P128">
+        <v>1.65</v>
+      </c>
+      <c r="Q128">
+        <v>1</v>
+      </c>
+      <c r="R128">
+        <v>7.6</v>
+      </c>
+      <c r="S128">
+        <v>0</v>
+      </c>
+      <c r="T128">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>94035000</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+      <c r="C129" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129" t="s">
+        <v>21</v>
+      </c>
+      <c r="E129">
+        <v>5102</v>
+      </c>
+      <c r="F129">
+        <v>5102</v>
+      </c>
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+      <c r="I129">
+        <v>3</v>
+      </c>
+      <c r="J129">
+        <v>17</v>
+      </c>
+      <c r="K129">
+        <v>53</v>
+      </c>
+      <c r="L129">
+        <v>999</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>1</v>
+      </c>
+      <c r="O129">
+        <v>1</v>
+      </c>
+      <c r="P129">
+        <v>1.65</v>
+      </c>
+      <c r="Q129">
+        <v>1</v>
+      </c>
+      <c r="R129">
+        <v>7.6</v>
+      </c>
+      <c r="S129">
+        <v>0</v>
+      </c>
+      <c r="T129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>94034000</v>
+      </c>
+      <c r="B130">
+        <v>0</v>
+      </c>
+      <c r="C130" t="s">
+        <v>20</v>
+      </c>
+      <c r="D130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E130">
+        <v>6108</v>
+      </c>
+      <c r="F130">
+        <v>6102</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <v>3</v>
+      </c>
+      <c r="J130">
+        <v>12</v>
+      </c>
+      <c r="K130">
+        <v>53</v>
+      </c>
+      <c r="L130">
+        <v>999</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>1</v>
+      </c>
+      <c r="O130">
+        <v>1</v>
+      </c>
+      <c r="P130">
+        <v>1.65</v>
+      </c>
+      <c r="Q130">
+        <v>1</v>
+      </c>
+      <c r="R130">
+        <v>7.6</v>
+      </c>
+      <c r="S130">
+        <v>0</v>
+      </c>
+      <c r="T130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>94034000</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+      <c r="C131" t="s">
+        <v>20</v>
+      </c>
+      <c r="D131" t="s">
+        <v>23</v>
+      </c>
+      <c r="E131">
+        <v>6108</v>
+      </c>
+      <c r="F131">
+        <v>6102</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>3</v>
+      </c>
+      <c r="J131">
+        <v>12</v>
+      </c>
+      <c r="K131">
+        <v>53</v>
+      </c>
+      <c r="L131">
+        <v>999</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>1</v>
+      </c>
+      <c r="O131">
+        <v>1</v>
+      </c>
+      <c r="P131">
+        <v>1.65</v>
+      </c>
+      <c r="Q131">
+        <v>1</v>
+      </c>
+      <c r="R131">
+        <v>7.6</v>
+      </c>
+      <c r="S131">
+        <v>0</v>
+      </c>
+      <c r="T131">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>94034000</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+      <c r="C132" t="s">
+        <v>20</v>
+      </c>
+      <c r="D132" t="s">
+        <v>21</v>
+      </c>
+      <c r="E132">
+        <v>6108</v>
+      </c>
+      <c r="F132">
+        <v>6102</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>3</v>
+      </c>
+      <c r="J132">
+        <v>12</v>
+      </c>
+      <c r="K132">
+        <v>53</v>
+      </c>
+      <c r="L132">
+        <v>999</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
+        <v>1</v>
+      </c>
+      <c r="O132">
+        <v>1</v>
+      </c>
+      <c r="P132">
+        <v>1.65</v>
+      </c>
+      <c r="Q132">
+        <v>1</v>
+      </c>
+      <c r="R132">
+        <v>7.6</v>
+      </c>
+      <c r="S132">
+        <v>0</v>
+      </c>
+      <c r="T132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>94034000</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+      <c r="C133" t="s">
+        <v>21</v>
+      </c>
+      <c r="D133" t="s">
+        <v>22</v>
+      </c>
+      <c r="E133">
+        <v>6108</v>
+      </c>
+      <c r="F133">
+        <v>6102</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>3</v>
+      </c>
+      <c r="J133">
+        <v>12</v>
+      </c>
+      <c r="K133">
+        <v>53</v>
+      </c>
+      <c r="L133">
+        <v>999</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>1</v>
+      </c>
+      <c r="O133">
+        <v>1</v>
+      </c>
+      <c r="P133">
+        <v>1.65</v>
+      </c>
+      <c r="Q133">
+        <v>1</v>
+      </c>
+      <c r="R133">
+        <v>7.6</v>
+      </c>
+      <c r="S133">
+        <v>0</v>
+      </c>
+      <c r="T133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <v>94034000</v>
+      </c>
+      <c r="B134">
+        <v>0</v>
+      </c>
+      <c r="C134" t="s">
+        <v>21</v>
+      </c>
+      <c r="D134" t="s">
+        <v>23</v>
+      </c>
+      <c r="E134">
+        <v>6108</v>
+      </c>
+      <c r="F134">
+        <v>6102</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>3</v>
+      </c>
+      <c r="J134">
+        <v>12</v>
+      </c>
+      <c r="K134">
+        <v>53</v>
+      </c>
+      <c r="L134">
+        <v>999</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>1</v>
+      </c>
+      <c r="O134">
+        <v>1</v>
+      </c>
+      <c r="P134">
+        <v>1.65</v>
+      </c>
+      <c r="Q134">
+        <v>1</v>
+      </c>
+      <c r="R134">
+        <v>7.6</v>
+      </c>
+      <c r="S134">
+        <v>0</v>
+      </c>
+      <c r="T134">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>94034000</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+      <c r="C135" t="s">
+        <v>21</v>
+      </c>
+      <c r="D135" t="s">
+        <v>21</v>
+      </c>
+      <c r="E135">
+        <v>5102</v>
+      </c>
+      <c r="F135">
+        <v>5102</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>3</v>
+      </c>
+      <c r="J135">
+        <v>17</v>
+      </c>
+      <c r="K135">
+        <v>53</v>
+      </c>
+      <c r="L135">
+        <v>999</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>1</v>
+      </c>
+      <c r="O135">
+        <v>1</v>
+      </c>
+      <c r="P135">
+        <v>1.65</v>
+      </c>
+      <c r="Q135">
+        <v>1</v>
+      </c>
+      <c r="R135">
+        <v>7.6</v>
+      </c>
+      <c r="S135">
+        <v>0</v>
+      </c>
+      <c r="T135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>94036000</v>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+      <c r="C136" t="s">
+        <v>20</v>
+      </c>
+      <c r="D136" t="s">
+        <v>22</v>
+      </c>
+      <c r="E136">
+        <v>6108</v>
+      </c>
+      <c r="F136">
+        <v>6102</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>3</v>
+      </c>
+      <c r="J136">
+        <v>12</v>
+      </c>
+      <c r="K136">
+        <v>53</v>
+      </c>
+      <c r="L136">
+        <v>999</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>1</v>
+      </c>
+      <c r="O136">
+        <v>1</v>
+      </c>
+      <c r="P136">
+        <v>1.65</v>
+      </c>
+      <c r="Q136">
+        <v>1</v>
+      </c>
+      <c r="R136">
+        <v>7.6</v>
+      </c>
+      <c r="S136">
+        <v>0</v>
+      </c>
+      <c r="T136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>94036000</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+      <c r="C137" t="s">
+        <v>20</v>
+      </c>
+      <c r="D137" t="s">
+        <v>23</v>
+      </c>
+      <c r="E137">
+        <v>6108</v>
+      </c>
+      <c r="F137">
+        <v>6102</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>3</v>
+      </c>
+      <c r="J137">
+        <v>12</v>
+      </c>
+      <c r="K137">
+        <v>53</v>
+      </c>
+      <c r="L137">
+        <v>999</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>1</v>
+      </c>
+      <c r="O137">
+        <v>1</v>
+      </c>
+      <c r="P137">
+        <v>1.65</v>
+      </c>
+      <c r="Q137">
+        <v>1</v>
+      </c>
+      <c r="R137">
+        <v>7.6</v>
+      </c>
+      <c r="S137">
+        <v>0</v>
+      </c>
+      <c r="T137">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>94036000</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+      <c r="C138" t="s">
+        <v>20</v>
+      </c>
+      <c r="D138" t="s">
+        <v>21</v>
+      </c>
+      <c r="E138">
+        <v>6108</v>
+      </c>
+      <c r="F138">
+        <v>6102</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>3</v>
+      </c>
+      <c r="J138">
+        <v>12</v>
+      </c>
+      <c r="K138">
+        <v>53</v>
+      </c>
+      <c r="L138">
+        <v>999</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>1</v>
+      </c>
+      <c r="O138">
+        <v>1</v>
+      </c>
+      <c r="P138">
+        <v>1.65</v>
+      </c>
+      <c r="Q138">
+        <v>1</v>
+      </c>
+      <c r="R138">
+        <v>7.6</v>
+      </c>
+      <c r="S138">
+        <v>0</v>
+      </c>
+      <c r="T138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>94036000</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+      <c r="C139" t="s">
+        <v>21</v>
+      </c>
+      <c r="D139" t="s">
+        <v>22</v>
+      </c>
+      <c r="E139">
+        <v>6108</v>
+      </c>
+      <c r="F139">
+        <v>6102</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>3</v>
+      </c>
+      <c r="J139">
+        <v>12</v>
+      </c>
+      <c r="K139">
+        <v>53</v>
+      </c>
+      <c r="L139">
+        <v>999</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>1</v>
+      </c>
+      <c r="O139">
+        <v>1</v>
+      </c>
+      <c r="P139">
+        <v>1.65</v>
+      </c>
+      <c r="Q139">
+        <v>1</v>
+      </c>
+      <c r="R139">
+        <v>7.6</v>
+      </c>
+      <c r="S139">
+        <v>0</v>
+      </c>
+      <c r="T139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>94036000</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+      <c r="C140" t="s">
+        <v>21</v>
+      </c>
+      <c r="D140" t="s">
+        <v>23</v>
+      </c>
+      <c r="E140">
+        <v>6108</v>
+      </c>
+      <c r="F140">
+        <v>6102</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>3</v>
+      </c>
+      <c r="J140">
+        <v>12</v>
+      </c>
+      <c r="K140">
+        <v>53</v>
+      </c>
+      <c r="L140">
+        <v>999</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>1</v>
+      </c>
+      <c r="O140">
+        <v>1</v>
+      </c>
+      <c r="P140">
+        <v>1.65</v>
+      </c>
+      <c r="Q140">
+        <v>1</v>
+      </c>
+      <c r="R140">
+        <v>7.6</v>
+      </c>
+      <c r="S140">
+        <v>0</v>
+      </c>
+      <c r="T140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>94036000</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+      <c r="C141" t="s">
+        <v>21</v>
+      </c>
+      <c r="D141" t="s">
+        <v>21</v>
+      </c>
+      <c r="E141">
+        <v>5102</v>
+      </c>
+      <c r="F141">
+        <v>5102</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <v>3</v>
+      </c>
+      <c r="J141">
+        <v>17</v>
+      </c>
+      <c r="K141">
+        <v>53</v>
+      </c>
+      <c r="L141">
+        <v>999</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>1</v>
+      </c>
+      <c r="O141">
+        <v>1</v>
+      </c>
+      <c r="P141">
+        <v>1.65</v>
+      </c>
+      <c r="Q141">
+        <v>1</v>
+      </c>
+      <c r="R141">
+        <v>7.6</v>
+      </c>
+      <c r="S141">
+        <v>0</v>
+      </c>
+      <c r="T141">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T107" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
+  <autoFilter ref="A1:T135" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
     <filterColumn colId="0">
       <filters>
-        <filter val="94044000"/>
+        <filter val="94036000"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/conf_fiscais.xlsx
+++ b/conf_fiscais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Faturamento\Desktop\nfe_sistema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71878AF-EF25-4737-9B9E-6E3EA3E6D1CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87ADAA61-1F95-40F6-A816-8881E4DAB16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F76E099-F64F-4C5B-B230-95152170BA2F}"/>
   </bookViews>
@@ -17,8 +17,8 @@
     <sheet name="Config ST" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Config Fiscal'!$A$1:$T$135</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Config ST'!$A$1:$F$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Config Fiscal'!$A$1:$T$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Config ST'!$A$1:$F$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="31">
   <si>
     <t>ncm</t>
   </si>
@@ -510,7 +510,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:T141"/>
+  <dimension ref="A1:T143"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -782,7 +782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>73211100</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>94036000</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>73211100</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>94036000</v>
       </c>
@@ -7044,7 +7044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>73211100</v>
       </c>
@@ -8904,7 +8904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>94036000</v>
       </c>
@@ -8966,7 +8966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>94036000</v>
       </c>
@@ -9028,7 +9028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>94036000</v>
       </c>
@@ -9090,7 +9090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>94036000</v>
       </c>
@@ -9152,7 +9152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>94036000</v>
       </c>
@@ -9214,7 +9214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>94036000</v>
       </c>
@@ -9276,11 +9276,135 @@
         <v>0</v>
       </c>
     </row>
+    <row r="142" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>73211100</v>
+      </c>
+      <c r="B142">
+        <v>1</v>
+      </c>
+      <c r="C142" t="s">
+        <v>20</v>
+      </c>
+      <c r="D142" t="s">
+        <v>22</v>
+      </c>
+      <c r="E142">
+        <v>6108</v>
+      </c>
+      <c r="F142">
+        <v>6102</v>
+      </c>
+      <c r="G142">
+        <v>60</v>
+      </c>
+      <c r="H142">
+        <v>60</v>
+      </c>
+      <c r="I142">
+        <v>3</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>53</v>
+      </c>
+      <c r="L142">
+        <v>999</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>1</v>
+      </c>
+      <c r="O142">
+        <v>1</v>
+      </c>
+      <c r="P142">
+        <v>1.65</v>
+      </c>
+      <c r="Q142">
+        <v>1</v>
+      </c>
+      <c r="R142">
+        <v>7.6</v>
+      </c>
+      <c r="S142">
+        <v>1</v>
+      </c>
+      <c r="T142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>73211100</v>
+      </c>
+      <c r="B143">
+        <v>1</v>
+      </c>
+      <c r="C143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D143" t="s">
+        <v>23</v>
+      </c>
+      <c r="E143">
+        <v>6108</v>
+      </c>
+      <c r="F143">
+        <v>6102</v>
+      </c>
+      <c r="G143">
+        <v>60</v>
+      </c>
+      <c r="H143">
+        <v>60</v>
+      </c>
+      <c r="I143">
+        <v>3</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>53</v>
+      </c>
+      <c r="L143">
+        <v>999</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>1</v>
+      </c>
+      <c r="O143">
+        <v>1</v>
+      </c>
+      <c r="P143">
+        <v>1.65</v>
+      </c>
+      <c r="Q143">
+        <v>1</v>
+      </c>
+      <c r="R143">
+        <v>7.6</v>
+      </c>
+      <c r="S143">
+        <v>1</v>
+      </c>
+      <c r="T143">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T135" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
+  <autoFilter ref="A1:T141" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
     <filterColumn colId="0">
       <filters>
-        <filter val="94036000"/>
+        <filter val="73211100"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -9292,7 +9416,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27418B64-EF4D-4086-9A4A-8537F5F99C12}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -9323,7 +9447,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>73211100</v>
       </c>
@@ -9343,7 +9467,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>73211100</v>
       </c>
@@ -9363,7 +9487,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>73211100</v>
       </c>
@@ -9423,7 +9547,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>84211210</v>
       </c>
@@ -9443,7 +9567,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>84211210</v>
       </c>
@@ -9783,7 +9907,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>73211100</v>
       </c>
@@ -9803,7 +9927,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>84211210</v>
       </c>
@@ -9823,11 +9947,51 @@
         <v>12</v>
       </c>
     </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>73211100</v>
+      </c>
+      <c r="B27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27">
+        <v>60.98</v>
+      </c>
+      <c r="E27">
+        <v>18</v>
+      </c>
+      <c r="F27">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>73211100</v>
+      </c>
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28">
+        <v>76.319999999999993</v>
+      </c>
+      <c r="E28">
+        <v>20</v>
+      </c>
+      <c r="F28">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F25" xr:uid="{27418B64-EF4D-4086-9A4A-8537F5F99C12}">
+  <autoFilter ref="A1:F26" xr:uid="{27418B64-EF4D-4086-9A4A-8537F5F99C12}">
     <filterColumn colId="0">
       <filters>
-        <filter val="84211210"/>
+        <filter val="73211100"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/conf_fiscais.xlsx
+++ b/conf_fiscais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Faturamento\Desktop\nfe_sistema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87ADAA61-1F95-40F6-A816-8881E4DAB16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00958FDC-EE29-4A07-AAF3-5E8E17C666FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F76E099-F64F-4C5B-B230-95152170BA2F}"/>
   </bookViews>
@@ -17,8 +17,8 @@
     <sheet name="Config ST" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Config Fiscal'!$A$1:$T$141</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Config ST'!$A$1:$F$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Config Fiscal'!$A$1:$T$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Config ST'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="31">
   <si>
     <t>ncm</t>
   </si>
@@ -510,7 +510,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:T143"/>
+  <dimension ref="A1:T149"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>84501900</v>
       </c>
@@ -782,7 +782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>73211100</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>73211100</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>84501900</v>
       </c>
@@ -7044,7 +7044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>73211100</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>73211100</v>
       </c>
@@ -9338,7 +9338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>73211100</v>
       </c>
@@ -9400,11 +9400,383 @@
         <v>2</v>
       </c>
     </row>
+    <row r="144" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>84501900</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+      <c r="C144" t="s">
+        <v>20</v>
+      </c>
+      <c r="D144" t="s">
+        <v>22</v>
+      </c>
+      <c r="E144">
+        <v>6108</v>
+      </c>
+      <c r="F144">
+        <v>6102</v>
+      </c>
+      <c r="G144">
+        <v>60</v>
+      </c>
+      <c r="H144">
+        <v>60</v>
+      </c>
+      <c r="I144">
+        <v>3</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>53</v>
+      </c>
+      <c r="L144">
+        <v>999</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
+      </c>
+      <c r="N144">
+        <v>1</v>
+      </c>
+      <c r="O144">
+        <v>1</v>
+      </c>
+      <c r="P144">
+        <v>1.65</v>
+      </c>
+      <c r="Q144">
+        <v>1</v>
+      </c>
+      <c r="R144">
+        <v>7.6</v>
+      </c>
+      <c r="S144">
+        <v>1</v>
+      </c>
+      <c r="T144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>84501900</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+      <c r="C145" t="s">
+        <v>20</v>
+      </c>
+      <c r="D145" t="s">
+        <v>23</v>
+      </c>
+      <c r="E145">
+        <v>6108</v>
+      </c>
+      <c r="F145">
+        <v>6102</v>
+      </c>
+      <c r="G145">
+        <v>60</v>
+      </c>
+      <c r="H145">
+        <v>60</v>
+      </c>
+      <c r="I145">
+        <v>3</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>53</v>
+      </c>
+      <c r="L145">
+        <v>999</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>1</v>
+      </c>
+      <c r="O145">
+        <v>1</v>
+      </c>
+      <c r="P145">
+        <v>1.65</v>
+      </c>
+      <c r="Q145">
+        <v>1</v>
+      </c>
+      <c r="R145">
+        <v>7.6</v>
+      </c>
+      <c r="S145">
+        <v>1</v>
+      </c>
+      <c r="T145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <v>84501900</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+      <c r="C146" t="s">
+        <v>20</v>
+      </c>
+      <c r="D146" t="s">
+        <v>21</v>
+      </c>
+      <c r="E146">
+        <v>6108</v>
+      </c>
+      <c r="F146">
+        <v>6102</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <v>3</v>
+      </c>
+      <c r="J146">
+        <v>12</v>
+      </c>
+      <c r="K146">
+        <v>53</v>
+      </c>
+      <c r="L146">
+        <v>999</v>
+      </c>
+      <c r="M146">
+        <v>0</v>
+      </c>
+      <c r="N146">
+        <v>1</v>
+      </c>
+      <c r="O146">
+        <v>1</v>
+      </c>
+      <c r="P146">
+        <v>1.65</v>
+      </c>
+      <c r="Q146">
+        <v>1</v>
+      </c>
+      <c r="R146">
+        <v>7.6</v>
+      </c>
+      <c r="S146">
+        <v>1</v>
+      </c>
+      <c r="T146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <v>84501900</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+      <c r="C147" t="s">
+        <v>21</v>
+      </c>
+      <c r="D147" t="s">
+        <v>22</v>
+      </c>
+      <c r="E147">
+        <v>6108</v>
+      </c>
+      <c r="F147">
+        <v>6102</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+      <c r="I147">
+        <v>3</v>
+      </c>
+      <c r="J147">
+        <v>12</v>
+      </c>
+      <c r="K147">
+        <v>53</v>
+      </c>
+      <c r="L147">
+        <v>999</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
+      </c>
+      <c r="N147">
+        <v>1</v>
+      </c>
+      <c r="O147">
+        <v>1</v>
+      </c>
+      <c r="P147">
+        <v>1.65</v>
+      </c>
+      <c r="Q147">
+        <v>1</v>
+      </c>
+      <c r="R147">
+        <v>7.6</v>
+      </c>
+      <c r="S147">
+        <v>1</v>
+      </c>
+      <c r="T147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <v>84501900</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+      <c r="C148" t="s">
+        <v>21</v>
+      </c>
+      <c r="D148" t="s">
+        <v>23</v>
+      </c>
+      <c r="E148">
+        <v>6108</v>
+      </c>
+      <c r="F148">
+        <v>6102</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148">
+        <v>3</v>
+      </c>
+      <c r="J148">
+        <v>12</v>
+      </c>
+      <c r="K148">
+        <v>53</v>
+      </c>
+      <c r="L148">
+        <v>999</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
+      </c>
+      <c r="N148">
+        <v>1</v>
+      </c>
+      <c r="O148">
+        <v>1</v>
+      </c>
+      <c r="P148">
+        <v>1.65</v>
+      </c>
+      <c r="Q148">
+        <v>1</v>
+      </c>
+      <c r="R148">
+        <v>7.6</v>
+      </c>
+      <c r="S148">
+        <v>1</v>
+      </c>
+      <c r="T148">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <v>84501900</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+      <c r="C149" t="s">
+        <v>21</v>
+      </c>
+      <c r="D149" t="s">
+        <v>21</v>
+      </c>
+      <c r="E149">
+        <v>6108</v>
+      </c>
+      <c r="F149">
+        <v>6102</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="I149">
+        <v>3</v>
+      </c>
+      <c r="J149">
+        <v>12</v>
+      </c>
+      <c r="K149">
+        <v>53</v>
+      </c>
+      <c r="L149">
+        <v>999</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
+      </c>
+      <c r="N149">
+        <v>1</v>
+      </c>
+      <c r="O149">
+        <v>1</v>
+      </c>
+      <c r="P149">
+        <v>1.65</v>
+      </c>
+      <c r="Q149">
+        <v>1</v>
+      </c>
+      <c r="R149">
+        <v>7.6</v>
+      </c>
+      <c r="S149">
+        <v>1</v>
+      </c>
+      <c r="T149">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T141" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
+  <autoFilter ref="A1:T146" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
     <filterColumn colId="0">
       <filters>
-        <filter val="73211100"/>
+        <filter val="84501900"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -9416,7 +9788,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27418B64-EF4D-4086-9A4A-8537F5F99C12}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -9447,7 +9819,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>73211100</v>
       </c>
@@ -9467,7 +9839,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>73211100</v>
       </c>
@@ -9487,7 +9859,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>73211100</v>
       </c>
@@ -9587,7 +9959,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>84501900</v>
       </c>
@@ -9607,7 +9979,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>84501900</v>
       </c>
@@ -9627,7 +9999,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>84501900</v>
       </c>
@@ -9907,7 +10279,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>73211100</v>
       </c>
@@ -9947,7 +10319,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>73211100</v>
       </c>
@@ -9967,7 +10339,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>73211100</v>
       </c>
@@ -9987,11 +10359,21 @@
         <v>12</v>
       </c>
     </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>84501900</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>84501900</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F26" xr:uid="{27418B64-EF4D-4086-9A4A-8537F5F99C12}">
+  <autoFilter ref="A1:F28" xr:uid="{27418B64-EF4D-4086-9A4A-8537F5F99C12}">
     <filterColumn colId="0">
       <filters>
-        <filter val="73211100"/>
+        <filter val="84501900"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/conf_fiscais.xlsx
+++ b/conf_fiscais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Faturamento\Desktop\nfe_sistema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00958FDC-EE29-4A07-AAF3-5E8E17C666FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0EFA1F6-0DCB-4711-ADE0-F12ACD70DFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F76E099-F64F-4C5B-B230-95152170BA2F}"/>
   </bookViews>
@@ -17,8 +17,8 @@
     <sheet name="Config ST" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Config Fiscal'!$A$1:$T$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Config ST'!$A$1:$F$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Config Fiscal'!$A$1:$T$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Config ST'!$A$1:$F$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="31">
   <si>
     <t>ncm</t>
   </si>
@@ -129,7 +129,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,6 +141,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -172,9 +179,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,8 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:T149"/>
+  <dimension ref="A1:T162"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -596,7 +605,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>84211210</v>
       </c>
@@ -658,7 +667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>84502090</v>
       </c>
@@ -782,7 +791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>73211100</v>
       </c>
@@ -844,7 +853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>94016100</v>
       </c>
@@ -906,7 +915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>94016100</v>
       </c>
@@ -968,7 +977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>94016100</v>
       </c>
@@ -1030,7 +1039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>94016100</v>
       </c>
@@ -1092,7 +1101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>94016100</v>
       </c>
@@ -1154,7 +1163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>94016100</v>
       </c>
@@ -1216,7 +1225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>84502020</v>
       </c>
@@ -1278,7 +1287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>84146000</v>
       </c>
@@ -1340,7 +1349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>84145990</v>
       </c>
@@ -1402,7 +1411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>84145990</v>
       </c>
@@ -1464,7 +1473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>84145990</v>
       </c>
@@ -1526,7 +1535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>84145990</v>
       </c>
@@ -1588,7 +1597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>84145990</v>
       </c>
@@ -1650,7 +1659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>84145110</v>
       </c>
@@ -1712,7 +1721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>84145110</v>
       </c>
@@ -1774,7 +1783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>84145110</v>
       </c>
@@ -1836,7 +1845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>94034000</v>
       </c>
@@ -1898,7 +1907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>94035000</v>
       </c>
@@ -1960,7 +1969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>94036000</v>
       </c>
@@ -2022,7 +2031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>73211100</v>
       </c>
@@ -2084,7 +2093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>84146000</v>
       </c>
@@ -2146,7 +2155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>84211210</v>
       </c>
@@ -2270,7 +2279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>84502020</v>
       </c>
@@ -2332,7 +2341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>84502090</v>
       </c>
@@ -2394,7 +2403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>94034000</v>
       </c>
@@ -2456,7 +2465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>94035000</v>
       </c>
@@ -2518,7 +2527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>94036000</v>
       </c>
@@ -2580,7 +2589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>94044000</v>
       </c>
@@ -2642,7 +2651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>94044000</v>
       </c>
@@ -2704,7 +2713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>94044000</v>
       </c>
@@ -2766,7 +2775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>94044000</v>
       </c>
@@ -2828,7 +2837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>94044000</v>
       </c>
@@ -2890,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>94044000</v>
       </c>
@@ -2952,7 +2961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>94044000</v>
       </c>
@@ -3014,7 +3023,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>94044000</v>
       </c>
@@ -3076,7 +3085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>94032010</v>
       </c>
@@ -3138,7 +3147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>94032010</v>
       </c>
@@ -3200,7 +3209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>94032010</v>
       </c>
@@ -3262,7 +3271,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>94032010</v>
       </c>
@@ -3324,7 +3333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>94032010</v>
       </c>
@@ -3386,7 +3395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>94032010</v>
       </c>
@@ -3448,7 +3457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>94049000</v>
       </c>
@@ -3510,7 +3519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>94049000</v>
       </c>
@@ -3572,7 +3581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>94049000</v>
       </c>
@@ -3634,7 +3643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>94049000</v>
       </c>
@@ -3696,7 +3705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>94049000</v>
       </c>
@@ -3758,7 +3767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>94049000</v>
       </c>
@@ -3820,7 +3829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>85167910</v>
       </c>
@@ -3882,7 +3891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>85167920</v>
       </c>
@@ -3944,7 +3953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>85094010</v>
       </c>
@@ -4006,7 +4015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>85094050</v>
       </c>
@@ -4068,7 +4077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>85167910</v>
       </c>
@@ -4130,7 +4139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>85167920</v>
       </c>
@@ -4192,7 +4201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>85094010</v>
       </c>
@@ -4254,7 +4263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>85094050</v>
       </c>
@@ -4316,7 +4325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>85167910</v>
       </c>
@@ -4378,7 +4387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>85167920</v>
       </c>
@@ -4440,7 +4449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>85094010</v>
       </c>
@@ -4502,7 +4511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>85094050</v>
       </c>
@@ -4564,7 +4573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>85167910</v>
       </c>
@@ -4626,7 +4635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>85167920</v>
       </c>
@@ -4688,7 +4697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>85094010</v>
       </c>
@@ -4750,7 +4759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>85094050</v>
       </c>
@@ -4812,7 +4821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>85167910</v>
       </c>
@@ -4874,7 +4883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>85167920</v>
       </c>
@@ -4936,7 +4945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>85094010</v>
       </c>
@@ -4998,7 +5007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>85094050</v>
       </c>
@@ -5060,7 +5069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>85167910</v>
       </c>
@@ -5122,7 +5131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>85167920</v>
       </c>
@@ -5184,7 +5193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>85094010</v>
       </c>
@@ -5246,7 +5255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>85094050</v>
       </c>
@@ -5308,7 +5317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>85167910</v>
       </c>
@@ -5370,7 +5379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>85167920</v>
       </c>
@@ -5432,7 +5441,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>85094010</v>
       </c>
@@ -5494,7 +5503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>85094050</v>
       </c>
@@ -5556,7 +5565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>85167910</v>
       </c>
@@ -5618,7 +5627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>85167920</v>
       </c>
@@ -5680,7 +5689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>85094010</v>
       </c>
@@ -5742,7 +5751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>85094050</v>
       </c>
@@ -5804,7 +5813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>84186931</v>
       </c>
@@ -5866,7 +5875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>84186931</v>
       </c>
@@ -5928,7 +5937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>84186931</v>
       </c>
@@ -5990,7 +5999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>84186931</v>
       </c>
@@ -6052,7 +6061,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>84186931</v>
       </c>
@@ -6114,7 +6123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>84186931</v>
       </c>
@@ -6176,7 +6185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>84186931</v>
       </c>
@@ -6238,7 +6247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>84186931</v>
       </c>
@@ -6300,7 +6309,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>84145190</v>
       </c>
@@ -6362,7 +6371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>84145190</v>
       </c>
@@ -6424,7 +6433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>84145190</v>
       </c>
@@ -6486,7 +6495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>84145190</v>
       </c>
@@ -6548,7 +6557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>84145190</v>
       </c>
@@ -6610,7 +6619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>84145190</v>
       </c>
@@ -6672,7 +6681,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>84145190</v>
       </c>
@@ -6734,7 +6743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>84145190</v>
       </c>
@@ -6796,7 +6805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>84145190</v>
       </c>
@@ -6858,7 +6867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>84145190</v>
       </c>
@@ -6920,7 +6929,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>84145190</v>
       </c>
@@ -6982,7 +6991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>84145190</v>
       </c>
@@ -7044,7 +7053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>73211100</v>
       </c>
@@ -7106,7 +7115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>84211210</v>
       </c>
@@ -7168,7 +7177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>94042900</v>
       </c>
@@ -7230,7 +7239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>94042900</v>
       </c>
@@ -7292,7 +7301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>94042900</v>
       </c>
@@ -7354,7 +7363,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>94042900</v>
       </c>
@@ -7416,7 +7425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>94042900</v>
       </c>
@@ -7478,7 +7487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>94042900</v>
       </c>
@@ -7540,7 +7549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>94042900</v>
       </c>
@@ -7602,7 +7611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>94042900</v>
       </c>
@@ -7664,7 +7673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>94041000</v>
       </c>
@@ -7726,7 +7735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>94041000</v>
       </c>
@@ -7788,7 +7797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>94041000</v>
       </c>
@@ -7850,7 +7859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>94041000</v>
       </c>
@@ -7912,7 +7921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>94041000</v>
       </c>
@@ -7974,7 +7983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>94041000</v>
       </c>
@@ -8036,7 +8045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>94041000</v>
       </c>
@@ -8098,7 +8107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>94041000</v>
       </c>
@@ -8160,7 +8169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>94035000</v>
       </c>
@@ -8222,7 +8231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>94035000</v>
       </c>
@@ -8284,7 +8293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>94035000</v>
       </c>
@@ -8346,7 +8355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>94035000</v>
       </c>
@@ -8408,7 +8417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>94035000</v>
       </c>
@@ -8470,7 +8479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>94035000</v>
       </c>
@@ -8532,7 +8541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>94034000</v>
       </c>
@@ -8594,7 +8603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>94034000</v>
       </c>
@@ -8656,7 +8665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>94034000</v>
       </c>
@@ -8718,7 +8727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>94034000</v>
       </c>
@@ -8780,7 +8789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>94034000</v>
       </c>
@@ -8842,7 +8851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>94034000</v>
       </c>
@@ -8904,7 +8913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>94036000</v>
       </c>
@@ -8966,7 +8975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>94036000</v>
       </c>
@@ -9028,7 +9037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>94036000</v>
       </c>
@@ -9090,7 +9099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>94036000</v>
       </c>
@@ -9152,7 +9161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>94036000</v>
       </c>
@@ -9214,7 +9223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>94036000</v>
       </c>
@@ -9276,7 +9285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>73211100</v>
       </c>
@@ -9338,7 +9347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>73211100</v>
       </c>
@@ -9580,7 +9589,7 @@
         <v>7.6</v>
       </c>
       <c r="S146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T146">
         <v>0</v>
@@ -9642,7 +9651,7 @@
         <v>7.6</v>
       </c>
       <c r="S147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T147">
         <v>0</v>
@@ -9704,7 +9713,7 @@
         <v>7.6</v>
       </c>
       <c r="S148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T148">
         <v>2</v>
@@ -9766,20 +9775,820 @@
         <v>7.6</v>
       </c>
       <c r="S149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T149">
         <v>0</v>
       </c>
     </row>
+    <row r="150" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <v>84502020</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+      <c r="C150" t="s">
+        <v>20</v>
+      </c>
+      <c r="D150" t="s">
+        <v>22</v>
+      </c>
+      <c r="E150">
+        <v>6108</v>
+      </c>
+      <c r="F150">
+        <v>6102</v>
+      </c>
+      <c r="G150">
+        <v>60</v>
+      </c>
+      <c r="H150">
+        <v>60</v>
+      </c>
+      <c r="I150">
+        <v>3</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>53</v>
+      </c>
+      <c r="L150">
+        <v>999</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
+      </c>
+      <c r="N150">
+        <v>1</v>
+      </c>
+      <c r="O150">
+        <v>1</v>
+      </c>
+      <c r="P150">
+        <v>1.65</v>
+      </c>
+      <c r="Q150">
+        <v>1</v>
+      </c>
+      <c r="R150">
+        <v>7.6</v>
+      </c>
+      <c r="S150">
+        <v>1</v>
+      </c>
+      <c r="T150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A151" s="2">
+        <v>94039100</v>
+      </c>
+      <c r="B151" s="2">
+        <v>0</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E151" s="2">
+        <v>6108</v>
+      </c>
+      <c r="F151" s="2">
+        <v>0</v>
+      </c>
+      <c r="G151" s="2">
+        <v>6102</v>
+      </c>
+      <c r="H151" s="2">
+        <v>0</v>
+      </c>
+      <c r="I151" s="2">
+        <v>3</v>
+      </c>
+      <c r="J151" s="2">
+        <v>12</v>
+      </c>
+      <c r="K151" s="2">
+        <v>53</v>
+      </c>
+      <c r="L151" s="2">
+        <v>999</v>
+      </c>
+      <c r="M151" s="2">
+        <v>0</v>
+      </c>
+      <c r="N151" s="2">
+        <v>1</v>
+      </c>
+      <c r="O151" s="2">
+        <v>1</v>
+      </c>
+      <c r="P151" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="Q151" s="2">
+        <v>1</v>
+      </c>
+      <c r="R151" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="S151">
+        <v>0</v>
+      </c>
+      <c r="T151" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A152" s="2">
+        <v>94039100</v>
+      </c>
+      <c r="B152" s="2">
+        <v>0</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E152" s="2">
+        <v>6108</v>
+      </c>
+      <c r="F152" s="2">
+        <v>0</v>
+      </c>
+      <c r="G152" s="2">
+        <v>6102</v>
+      </c>
+      <c r="H152" s="2">
+        <v>0</v>
+      </c>
+      <c r="I152" s="2">
+        <v>3</v>
+      </c>
+      <c r="J152" s="2">
+        <v>12</v>
+      </c>
+      <c r="K152" s="2">
+        <v>53</v>
+      </c>
+      <c r="L152" s="2">
+        <v>999</v>
+      </c>
+      <c r="M152" s="2">
+        <v>0</v>
+      </c>
+      <c r="N152" s="2">
+        <v>1</v>
+      </c>
+      <c r="O152" s="2">
+        <v>1</v>
+      </c>
+      <c r="P152" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="Q152" s="2">
+        <v>1</v>
+      </c>
+      <c r="R152" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="S152">
+        <v>0</v>
+      </c>
+      <c r="T152" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A153" s="2">
+        <v>94039100</v>
+      </c>
+      <c r="B153" s="2">
+        <v>0</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E153" s="2">
+        <v>5102</v>
+      </c>
+      <c r="F153" s="2">
+        <v>0</v>
+      </c>
+      <c r="G153" s="2">
+        <v>5102</v>
+      </c>
+      <c r="H153" s="2">
+        <v>0</v>
+      </c>
+      <c r="I153" s="2">
+        <v>3</v>
+      </c>
+      <c r="J153" s="2">
+        <v>12</v>
+      </c>
+      <c r="K153" s="2">
+        <v>53</v>
+      </c>
+      <c r="L153" s="2">
+        <v>999</v>
+      </c>
+      <c r="M153" s="2">
+        <v>0</v>
+      </c>
+      <c r="N153" s="2">
+        <v>1</v>
+      </c>
+      <c r="O153" s="2">
+        <v>1</v>
+      </c>
+      <c r="P153" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="Q153" s="2">
+        <v>1</v>
+      </c>
+      <c r="R153" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="S153">
+        <v>0</v>
+      </c>
+      <c r="T153" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A154" s="2">
+        <v>94039100</v>
+      </c>
+      <c r="B154" s="2">
+        <v>0</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E154" s="2">
+        <v>6108</v>
+      </c>
+      <c r="F154" s="2">
+        <v>0</v>
+      </c>
+      <c r="G154" s="2">
+        <v>6102</v>
+      </c>
+      <c r="H154" s="2">
+        <v>0</v>
+      </c>
+      <c r="I154" s="2">
+        <v>3</v>
+      </c>
+      <c r="J154" s="2">
+        <v>12</v>
+      </c>
+      <c r="K154" s="2">
+        <v>53</v>
+      </c>
+      <c r="L154" s="2">
+        <v>999</v>
+      </c>
+      <c r="M154" s="2">
+        <v>0</v>
+      </c>
+      <c r="N154" s="2">
+        <v>1</v>
+      </c>
+      <c r="O154" s="2">
+        <v>1</v>
+      </c>
+      <c r="P154" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="Q154" s="2">
+        <v>1</v>
+      </c>
+      <c r="R154" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="S154">
+        <v>0</v>
+      </c>
+      <c r="T154" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A155" s="2">
+        <v>94039100</v>
+      </c>
+      <c r="B155" s="2">
+        <v>0</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E155" s="2">
+        <v>6108</v>
+      </c>
+      <c r="F155" s="2">
+        <v>0</v>
+      </c>
+      <c r="G155" s="2">
+        <v>6102</v>
+      </c>
+      <c r="H155" s="2">
+        <v>0</v>
+      </c>
+      <c r="I155" s="2">
+        <v>3</v>
+      </c>
+      <c r="J155" s="2">
+        <v>12</v>
+      </c>
+      <c r="K155" s="2">
+        <v>53</v>
+      </c>
+      <c r="L155" s="2">
+        <v>999</v>
+      </c>
+      <c r="M155" s="2">
+        <v>0</v>
+      </c>
+      <c r="N155" s="2">
+        <v>1</v>
+      </c>
+      <c r="O155" s="2">
+        <v>1</v>
+      </c>
+      <c r="P155" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="Q155" s="2">
+        <v>1</v>
+      </c>
+      <c r="R155" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="S155">
+        <v>0</v>
+      </c>
+      <c r="T155" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A156" s="2">
+        <v>94039100</v>
+      </c>
+      <c r="B156" s="2">
+        <v>0</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E156" s="2">
+        <v>6108</v>
+      </c>
+      <c r="F156" s="2">
+        <v>0</v>
+      </c>
+      <c r="G156" s="2">
+        <v>6102</v>
+      </c>
+      <c r="H156" s="2">
+        <v>0</v>
+      </c>
+      <c r="I156" s="2">
+        <v>3</v>
+      </c>
+      <c r="J156" s="2">
+        <v>7</v>
+      </c>
+      <c r="K156" s="2">
+        <v>53</v>
+      </c>
+      <c r="L156" s="2">
+        <v>999</v>
+      </c>
+      <c r="M156" s="2">
+        <v>0</v>
+      </c>
+      <c r="N156" s="2">
+        <v>1</v>
+      </c>
+      <c r="O156" s="2">
+        <v>1</v>
+      </c>
+      <c r="P156" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="Q156" s="2">
+        <v>1</v>
+      </c>
+      <c r="R156" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="S156">
+        <v>0</v>
+      </c>
+      <c r="T156" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A157" s="2">
+        <v>94039100</v>
+      </c>
+      <c r="B157" s="2">
+        <v>0</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E157" s="2">
+        <v>6108</v>
+      </c>
+      <c r="F157" s="2">
+        <v>0</v>
+      </c>
+      <c r="G157" s="2">
+        <v>6102</v>
+      </c>
+      <c r="H157" s="2">
+        <v>0</v>
+      </c>
+      <c r="I157" s="2">
+        <v>3</v>
+      </c>
+      <c r="J157" s="2">
+        <v>12</v>
+      </c>
+      <c r="K157" s="2">
+        <v>53</v>
+      </c>
+      <c r="L157" s="2">
+        <v>999</v>
+      </c>
+      <c r="M157" s="2">
+        <v>0</v>
+      </c>
+      <c r="N157" s="2">
+        <v>1</v>
+      </c>
+      <c r="O157" s="2">
+        <v>1</v>
+      </c>
+      <c r="P157" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="Q157" s="2">
+        <v>1</v>
+      </c>
+      <c r="R157" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="S157">
+        <v>0</v>
+      </c>
+      <c r="T157" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A158" s="2">
+        <v>94039100</v>
+      </c>
+      <c r="B158" s="2">
+        <v>0</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E158" s="2">
+        <v>6108</v>
+      </c>
+      <c r="F158" s="2">
+        <v>0</v>
+      </c>
+      <c r="G158" s="2">
+        <v>6102</v>
+      </c>
+      <c r="H158" s="2">
+        <v>0</v>
+      </c>
+      <c r="I158" s="2">
+        <v>3</v>
+      </c>
+      <c r="J158" s="2">
+        <v>12</v>
+      </c>
+      <c r="K158" s="2">
+        <v>53</v>
+      </c>
+      <c r="L158" s="2">
+        <v>999</v>
+      </c>
+      <c r="M158" s="2">
+        <v>0</v>
+      </c>
+      <c r="N158" s="2">
+        <v>1</v>
+      </c>
+      <c r="O158" s="2">
+        <v>1</v>
+      </c>
+      <c r="P158" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="Q158" s="2">
+        <v>1</v>
+      </c>
+      <c r="R158" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="S158">
+        <v>0</v>
+      </c>
+      <c r="T158" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A159" s="2">
+        <v>94039100</v>
+      </c>
+      <c r="B159" s="2">
+        <v>0</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E159" s="2">
+        <v>6108</v>
+      </c>
+      <c r="F159" s="2">
+        <v>0</v>
+      </c>
+      <c r="G159" s="2">
+        <v>6102</v>
+      </c>
+      <c r="H159" s="2">
+        <v>0</v>
+      </c>
+      <c r="I159" s="2">
+        <v>3</v>
+      </c>
+      <c r="J159" s="2">
+        <v>7</v>
+      </c>
+      <c r="K159" s="2">
+        <v>53</v>
+      </c>
+      <c r="L159" s="2">
+        <v>999</v>
+      </c>
+      <c r="M159" s="2">
+        <v>0</v>
+      </c>
+      <c r="N159" s="2">
+        <v>1</v>
+      </c>
+      <c r="O159" s="2">
+        <v>1</v>
+      </c>
+      <c r="P159" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="Q159" s="2">
+        <v>1</v>
+      </c>
+      <c r="R159" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="S159">
+        <v>0</v>
+      </c>
+      <c r="T159" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A160" s="2">
+        <v>94039100</v>
+      </c>
+      <c r="B160" s="2">
+        <v>0</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E160" s="2">
+        <v>6108</v>
+      </c>
+      <c r="F160" s="2">
+        <v>0</v>
+      </c>
+      <c r="G160" s="2">
+        <v>6102</v>
+      </c>
+      <c r="H160" s="2">
+        <v>0</v>
+      </c>
+      <c r="I160" s="2">
+        <v>3</v>
+      </c>
+      <c r="J160" s="2">
+        <v>7</v>
+      </c>
+      <c r="K160" s="2">
+        <v>53</v>
+      </c>
+      <c r="L160" s="2">
+        <v>999</v>
+      </c>
+      <c r="M160" s="2">
+        <v>0</v>
+      </c>
+      <c r="N160" s="2">
+        <v>1</v>
+      </c>
+      <c r="O160" s="2">
+        <v>1</v>
+      </c>
+      <c r="P160" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="Q160" s="2">
+        <v>1</v>
+      </c>
+      <c r="R160" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="S160">
+        <v>0</v>
+      </c>
+      <c r="T160" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A161" s="2">
+        <v>94039100</v>
+      </c>
+      <c r="B161" s="2">
+        <v>0</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E161" s="2">
+        <v>6108</v>
+      </c>
+      <c r="F161" s="2">
+        <v>0</v>
+      </c>
+      <c r="G161" s="2">
+        <v>6102</v>
+      </c>
+      <c r="H161" s="2">
+        <v>0</v>
+      </c>
+      <c r="I161" s="2">
+        <v>3</v>
+      </c>
+      <c r="J161" s="2">
+        <v>7</v>
+      </c>
+      <c r="K161" s="2">
+        <v>53</v>
+      </c>
+      <c r="L161" s="2">
+        <v>999</v>
+      </c>
+      <c r="M161" s="2">
+        <v>0</v>
+      </c>
+      <c r="N161" s="2">
+        <v>1</v>
+      </c>
+      <c r="O161" s="2">
+        <v>1</v>
+      </c>
+      <c r="P161" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="Q161" s="2">
+        <v>1</v>
+      </c>
+      <c r="R161" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="S161">
+        <v>0</v>
+      </c>
+      <c r="T161" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A162" s="2">
+        <v>94039100</v>
+      </c>
+      <c r="B162" s="2">
+        <v>0</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E162" s="2">
+        <v>5102</v>
+      </c>
+      <c r="F162" s="2">
+        <v>0</v>
+      </c>
+      <c r="G162" s="2">
+        <v>5102</v>
+      </c>
+      <c r="H162" s="2">
+        <v>0</v>
+      </c>
+      <c r="I162" s="2">
+        <v>3</v>
+      </c>
+      <c r="J162" s="2">
+        <v>17</v>
+      </c>
+      <c r="K162" s="2">
+        <v>53</v>
+      </c>
+      <c r="L162" s="2">
+        <v>999</v>
+      </c>
+      <c r="M162" s="2">
+        <v>0</v>
+      </c>
+      <c r="N162" s="2">
+        <v>1</v>
+      </c>
+      <c r="O162" s="2">
+        <v>1</v>
+      </c>
+      <c r="P162" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="Q162" s="2">
+        <v>1</v>
+      </c>
+      <c r="R162" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="S162">
+        <v>0</v>
+      </c>
+      <c r="T162" s="2">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T146" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="84501900"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:T152" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -9959,7 +10768,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>84501900</v>
       </c>
@@ -9979,7 +10788,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>84501900</v>
       </c>
@@ -9999,7 +10808,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>84501900</v>
       </c>
@@ -10019,7 +10828,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>84502020</v>
       </c>
@@ -10039,7 +10848,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>84502020</v>
       </c>
@@ -10359,21 +11168,51 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>84501900</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29">
+        <v>87.1</v>
+      </c>
+      <c r="E29">
+        <v>22</v>
+      </c>
+      <c r="F29">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>84501900</v>
       </c>
+      <c r="B30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30">
+        <v>55.61</v>
+      </c>
+      <c r="E30">
+        <v>18</v>
+      </c>
+      <c r="F30">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F28" xr:uid="{27418B64-EF4D-4086-9A4A-8537F5F99C12}">
+  <autoFilter ref="A1:F30" xr:uid="{27418B64-EF4D-4086-9A4A-8537F5F99C12}">
     <filterColumn colId="0">
       <filters>
-        <filter val="84501900"/>
+        <filter val="84502020"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/conf_fiscais.xlsx
+++ b/conf_fiscais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Faturamento\Desktop\nfe_sistema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0EFA1F6-0DCB-4711-ADE0-F12ACD70DFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20FA648-35C4-4016-B097-380385B2423C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F76E099-F64F-4C5B-B230-95152170BA2F}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Config ST" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Config Fiscal'!$A$1:$T$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Config Fiscal'!$A$1:$U$162</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Config ST'!$A$1:$F$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="34">
   <si>
     <t>ncm</t>
   </si>
@@ -123,6 +123,15 @@
   </si>
   <si>
     <t>AM</t>
+  </si>
+  <si>
+    <t>tipo_operacao</t>
+  </si>
+  <si>
+    <t>INTERNA</t>
+  </si>
+  <si>
+    <t>INTERESTADUAL</t>
   </si>
 </sst>
 </file>
@@ -519,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
-  <dimension ref="A1:T162"/>
+  <dimension ref="A1:U162"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -541,9 +550,10 @@
     <col min="18" max="18" width="6.5546875" customWidth="1"/>
     <col min="19" max="19" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -604,8 +614,11 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>84211210</v>
       </c>
@@ -666,8 +679,11 @@
       <c r="T2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>84502090</v>
       </c>
@@ -728,8 +744,11 @@
       <c r="T3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>84501900</v>
       </c>
@@ -790,8 +809,11 @@
       <c r="T4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>73211100</v>
       </c>
@@ -852,8 +874,11 @@
       <c r="T5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>94016100</v>
       </c>
@@ -914,8 +939,11 @@
       <c r="T6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>94016100</v>
       </c>
@@ -976,8 +1004,11 @@
       <c r="T7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>94016100</v>
       </c>
@@ -1038,8 +1069,11 @@
       <c r="T8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>94016100</v>
       </c>
@@ -1100,8 +1134,11 @@
       <c r="T9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>94016100</v>
       </c>
@@ -1162,8 +1199,11 @@
       <c r="T10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>94016100</v>
       </c>
@@ -1224,8 +1264,11 @@
       <c r="T11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>84502020</v>
       </c>
@@ -1286,8 +1329,11 @@
       <c r="T12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>84146000</v>
       </c>
@@ -1348,8 +1394,11 @@
       <c r="T13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>84145990</v>
       </c>
@@ -1410,8 +1459,11 @@
       <c r="T14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>84145990</v>
       </c>
@@ -1472,8 +1524,11 @@
       <c r="T15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>84145990</v>
       </c>
@@ -1534,8 +1589,11 @@
       <c r="T16">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>84145990</v>
       </c>
@@ -1596,8 +1654,11 @@
       <c r="T17">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>84145990</v>
       </c>
@@ -1658,8 +1719,11 @@
       <c r="T18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>84145110</v>
       </c>
@@ -1720,8 +1784,11 @@
       <c r="T19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>84145110</v>
       </c>
@@ -1782,8 +1849,11 @@
       <c r="T20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>84145110</v>
       </c>
@@ -1844,8 +1914,11 @@
       <c r="T21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>94034000</v>
       </c>
@@ -1906,8 +1979,11 @@
       <c r="T22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>94035000</v>
       </c>
@@ -1968,8 +2044,11 @@
       <c r="T23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>94036000</v>
       </c>
@@ -2030,8 +2109,11 @@
       <c r="T24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>73211100</v>
       </c>
@@ -2092,8 +2174,11 @@
       <c r="T25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U25" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>84146000</v>
       </c>
@@ -2154,8 +2239,11 @@
       <c r="T26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U26" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>84211210</v>
       </c>
@@ -2216,8 +2304,11 @@
       <c r="T27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>84501900</v>
       </c>
@@ -2278,8 +2369,11 @@
       <c r="T28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>84502020</v>
       </c>
@@ -2340,8 +2434,11 @@
       <c r="T29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>84502090</v>
       </c>
@@ -2402,8 +2499,11 @@
       <c r="T30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>94034000</v>
       </c>
@@ -2464,8 +2564,11 @@
       <c r="T31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U31" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>94035000</v>
       </c>
@@ -2526,8 +2629,11 @@
       <c r="T32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U32" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>94036000</v>
       </c>
@@ -2588,8 +2694,11 @@
       <c r="T33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>94044000</v>
       </c>
@@ -2650,8 +2759,11 @@
       <c r="T34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>94044000</v>
       </c>
@@ -2712,8 +2824,11 @@
       <c r="T35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>94044000</v>
       </c>
@@ -2774,8 +2889,11 @@
       <c r="T36">
         <v>2</v>
       </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>94044000</v>
       </c>
@@ -2836,8 +2954,11 @@
       <c r="T37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>94044000</v>
       </c>
@@ -2898,8 +3019,11 @@
       <c r="T38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U38" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>94044000</v>
       </c>
@@ -2960,8 +3084,11 @@
       <c r="T39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U39" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>94044000</v>
       </c>
@@ -3022,8 +3149,11 @@
       <c r="T40">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U40" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>94044000</v>
       </c>
@@ -3084,8 +3214,11 @@
       <c r="T41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U41" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>94032010</v>
       </c>
@@ -3146,8 +3279,11 @@
       <c r="T42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U42" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>94032010</v>
       </c>
@@ -3208,8 +3344,11 @@
       <c r="T43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U43" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>94032010</v>
       </c>
@@ -3270,8 +3409,11 @@
       <c r="T44">
         <v>2</v>
       </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U44" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>94032010</v>
       </c>
@@ -3332,8 +3474,11 @@
       <c r="T45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U45" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>94032010</v>
       </c>
@@ -3394,8 +3539,11 @@
       <c r="T46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U46" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>94032010</v>
       </c>
@@ -3456,8 +3604,11 @@
       <c r="T47">
         <v>2</v>
       </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U47" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>94049000</v>
       </c>
@@ -3518,8 +3669,11 @@
       <c r="T48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U48" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>94049000</v>
       </c>
@@ -3580,8 +3734,11 @@
       <c r="T49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U49" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>94049000</v>
       </c>
@@ -3642,8 +3799,11 @@
       <c r="T50">
         <v>2</v>
       </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U50" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>94049000</v>
       </c>
@@ -3704,8 +3864,11 @@
       <c r="T51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U51" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>94049000</v>
       </c>
@@ -3766,8 +3929,11 @@
       <c r="T52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U52" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>94049000</v>
       </c>
@@ -3828,8 +3994,11 @@
       <c r="T53">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U53" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>85167910</v>
       </c>
@@ -3890,8 +4059,11 @@
       <c r="T54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U54" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>85167920</v>
       </c>
@@ -3952,8 +4124,11 @@
       <c r="T55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U55" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>85094010</v>
       </c>
@@ -4014,8 +4189,11 @@
       <c r="T56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U56" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>85094050</v>
       </c>
@@ -4076,8 +4254,11 @@
       <c r="T57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U57" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>85167910</v>
       </c>
@@ -4138,8 +4319,11 @@
       <c r="T58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U58" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>85167920</v>
       </c>
@@ -4200,8 +4384,11 @@
       <c r="T59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U59" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>85094010</v>
       </c>
@@ -4262,8 +4449,11 @@
       <c r="T60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U60" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>85094050</v>
       </c>
@@ -4324,8 +4514,11 @@
       <c r="T61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U61" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>85167910</v>
       </c>
@@ -4386,8 +4579,11 @@
       <c r="T62">
         <v>2</v>
       </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U62" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>85167920</v>
       </c>
@@ -4448,8 +4644,11 @@
       <c r="T63">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U63" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>85094010</v>
       </c>
@@ -4510,8 +4709,11 @@
       <c r="T64">
         <v>2</v>
       </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U64" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>85094050</v>
       </c>
@@ -4572,8 +4774,11 @@
       <c r="T65">
         <v>2</v>
       </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U65" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>85167910</v>
       </c>
@@ -4634,8 +4839,11 @@
       <c r="T66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U66" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>85167920</v>
       </c>
@@ -4696,8 +4904,11 @@
       <c r="T67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U67" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>85094010</v>
       </c>
@@ -4758,8 +4969,11 @@
       <c r="T68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U68" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>85094050</v>
       </c>
@@ -4820,8 +5034,11 @@
       <c r="T69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U69" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>85167910</v>
       </c>
@@ -4882,8 +5099,11 @@
       <c r="T70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U70" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>85167920</v>
       </c>
@@ -4944,8 +5164,11 @@
       <c r="T71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U71" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>85094010</v>
       </c>
@@ -5006,8 +5229,11 @@
       <c r="T72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U72" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>85094050</v>
       </c>
@@ -5068,8 +5294,11 @@
       <c r="T73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U73" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>85167910</v>
       </c>
@@ -5130,8 +5359,11 @@
       <c r="T74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U74" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>85167920</v>
       </c>
@@ -5192,8 +5424,11 @@
       <c r="T75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U75" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>85094010</v>
       </c>
@@ -5254,8 +5489,11 @@
       <c r="T76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U76" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>85094050</v>
       </c>
@@ -5316,8 +5554,11 @@
       <c r="T77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U77" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>85167910</v>
       </c>
@@ -5378,8 +5619,11 @@
       <c r="T78">
         <v>2</v>
       </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U78" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>85167920</v>
       </c>
@@ -5440,8 +5684,11 @@
       <c r="T79">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U79" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>85094010</v>
       </c>
@@ -5502,8 +5749,11 @@
       <c r="T80">
         <v>2</v>
       </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U80" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>85094050</v>
       </c>
@@ -5564,8 +5814,11 @@
       <c r="T81">
         <v>2</v>
       </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U81" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>85167910</v>
       </c>
@@ -5626,8 +5879,11 @@
       <c r="T82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U82" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>85167920</v>
       </c>
@@ -5688,8 +5944,11 @@
       <c r="T83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U83" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>85094010</v>
       </c>
@@ -5750,8 +6009,11 @@
       <c r="T84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U84" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>85094050</v>
       </c>
@@ -5812,8 +6074,11 @@
       <c r="T85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U85" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>84186931</v>
       </c>
@@ -5874,8 +6139,11 @@
       <c r="T86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U86" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>84186931</v>
       </c>
@@ -5936,8 +6204,11 @@
       <c r="T87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U87" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>84186931</v>
       </c>
@@ -5998,8 +6269,11 @@
       <c r="T88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U88" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>84186931</v>
       </c>
@@ -6060,8 +6334,11 @@
       <c r="T89">
         <v>2</v>
       </c>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U89" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>84186931</v>
       </c>
@@ -6122,8 +6399,11 @@
       <c r="T90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U90" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>84186931</v>
       </c>
@@ -6184,8 +6464,11 @@
       <c r="T91">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U91" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>84186931</v>
       </c>
@@ -6246,8 +6529,11 @@
       <c r="T92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U92" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>84186931</v>
       </c>
@@ -6308,8 +6594,11 @@
       <c r="T93">
         <v>2</v>
       </c>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U93" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>84145190</v>
       </c>
@@ -6370,8 +6659,11 @@
       <c r="T94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U94" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>84145190</v>
       </c>
@@ -6432,8 +6724,11 @@
       <c r="T95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U95" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>84145190</v>
       </c>
@@ -6494,8 +6789,11 @@
       <c r="T96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U96" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>84145190</v>
       </c>
@@ -6556,8 +6854,11 @@
       <c r="T97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U97" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>84145190</v>
       </c>
@@ -6618,8 +6919,11 @@
       <c r="T98">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U98" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>84145190</v>
       </c>
@@ -6680,8 +6984,11 @@
       <c r="T99">
         <v>2</v>
       </c>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U99" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>84145190</v>
       </c>
@@ -6742,8 +7049,11 @@
       <c r="T100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U100" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>84145190</v>
       </c>
@@ -6804,8 +7114,11 @@
       <c r="T101">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U101" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>84145190</v>
       </c>
@@ -6866,8 +7179,11 @@
       <c r="T102">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U102" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>84145190</v>
       </c>
@@ -6928,8 +7244,11 @@
       <c r="T103">
         <v>2</v>
       </c>
-    </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U103" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>84145190</v>
       </c>
@@ -6990,8 +7309,11 @@
       <c r="T104">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U104" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>84145190</v>
       </c>
@@ -7052,8 +7374,11 @@
       <c r="T105">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U105" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>73211100</v>
       </c>
@@ -7114,8 +7439,11 @@
       <c r="T106">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U106" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>84211210</v>
       </c>
@@ -7176,8 +7504,11 @@
       <c r="T107">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U107" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>94042900</v>
       </c>
@@ -7238,8 +7569,11 @@
       <c r="T108">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U108" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>94042900</v>
       </c>
@@ -7300,8 +7634,11 @@
       <c r="T109">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U109" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>94042900</v>
       </c>
@@ -7362,8 +7699,11 @@
       <c r="T110">
         <v>2</v>
       </c>
-    </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U110" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>94042900</v>
       </c>
@@ -7424,8 +7764,11 @@
       <c r="T111">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U111" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>94042900</v>
       </c>
@@ -7486,8 +7829,11 @@
       <c r="T112">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U112" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>94042900</v>
       </c>
@@ -7548,8 +7894,11 @@
       <c r="T113">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U113" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>94042900</v>
       </c>
@@ -7610,8 +7959,11 @@
       <c r="T114">
         <v>2</v>
       </c>
-    </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U114" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>94042900</v>
       </c>
@@ -7672,8 +8024,11 @@
       <c r="T115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U115" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>94041000</v>
       </c>
@@ -7734,8 +8089,11 @@
       <c r="T116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U116" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>94041000</v>
       </c>
@@ -7796,8 +8154,11 @@
       <c r="T117">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U117" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>94041000</v>
       </c>
@@ -7858,8 +8219,11 @@
       <c r="T118">
         <v>2</v>
       </c>
-    </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U118" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>94041000</v>
       </c>
@@ -7920,8 +8284,11 @@
       <c r="T119">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U119" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>94041000</v>
       </c>
@@ -7982,8 +8349,11 @@
       <c r="T120">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U120" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>94041000</v>
       </c>
@@ -8044,8 +8414,11 @@
       <c r="T121">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U121" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>94041000</v>
       </c>
@@ -8106,8 +8479,11 @@
       <c r="T122">
         <v>2</v>
       </c>
-    </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U122" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>94041000</v>
       </c>
@@ -8168,8 +8544,11 @@
       <c r="T123">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U123" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>94035000</v>
       </c>
@@ -8230,8 +8609,11 @@
       <c r="T124">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U124" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>94035000</v>
       </c>
@@ -8292,8 +8674,11 @@
       <c r="T125">
         <v>2</v>
       </c>
-    </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U125" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>94035000</v>
       </c>
@@ -8354,8 +8739,11 @@
       <c r="T126">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U126" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>94035000</v>
       </c>
@@ -8416,8 +8804,11 @@
       <c r="T127">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U127" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>94035000</v>
       </c>
@@ -8478,8 +8869,11 @@
       <c r="T128">
         <v>2</v>
       </c>
-    </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U128" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>94035000</v>
       </c>
@@ -8540,8 +8934,11 @@
       <c r="T129">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U129" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>94034000</v>
       </c>
@@ -8602,8 +8999,11 @@
       <c r="T130">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U130" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>94034000</v>
       </c>
@@ -8664,8 +9064,11 @@
       <c r="T131">
         <v>2</v>
       </c>
-    </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U131" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>94034000</v>
       </c>
@@ -8726,8 +9129,11 @@
       <c r="T132">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U132" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>94034000</v>
       </c>
@@ -8788,8 +9194,11 @@
       <c r="T133">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U133" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>94034000</v>
       </c>
@@ -8850,8 +9259,11 @@
       <c r="T134">
         <v>2</v>
       </c>
-    </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U134" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>94034000</v>
       </c>
@@ -8912,8 +9324,11 @@
       <c r="T135">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U135" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>94036000</v>
       </c>
@@ -8974,8 +9389,11 @@
       <c r="T136">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U136" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>94036000</v>
       </c>
@@ -9036,8 +9454,11 @@
       <c r="T137">
         <v>2</v>
       </c>
-    </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U137" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>94036000</v>
       </c>
@@ -9098,8 +9519,11 @@
       <c r="T138">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U138" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>94036000</v>
       </c>
@@ -9160,8 +9584,11 @@
       <c r="T139">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U139" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>94036000</v>
       </c>
@@ -9222,8 +9649,11 @@
       <c r="T140">
         <v>2</v>
       </c>
-    </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U140" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>94036000</v>
       </c>
@@ -9284,8 +9714,11 @@
       <c r="T141">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U141" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>73211100</v>
       </c>
@@ -9346,8 +9779,11 @@
       <c r="T142">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U142" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>73211100</v>
       </c>
@@ -9408,8 +9844,11 @@
       <c r="T143">
         <v>2</v>
       </c>
-    </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U143" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>84501900</v>
       </c>
@@ -9470,8 +9909,11 @@
       <c r="T144">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U144" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>84501900</v>
       </c>
@@ -9532,8 +9974,11 @@
       <c r="T145">
         <v>2</v>
       </c>
-    </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U145" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>84501900</v>
       </c>
@@ -9594,8 +10039,11 @@
       <c r="T146">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U146" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>84501900</v>
       </c>
@@ -9656,8 +10104,11 @@
       <c r="T147">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U147" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="148" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>84501900</v>
       </c>
@@ -9718,8 +10169,11 @@
       <c r="T148">
         <v>2</v>
       </c>
-    </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U148" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>84501900</v>
       </c>
@@ -9780,8 +10234,11 @@
       <c r="T149">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U149" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>84502020</v>
       </c>
@@ -9842,8 +10299,11 @@
       <c r="T150">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U150" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>94039100</v>
       </c>
@@ -9904,8 +10364,11 @@
       <c r="T151" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U151" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="152" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>94039100</v>
       </c>
@@ -9966,8 +10429,11 @@
       <c r="T152" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U152" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="153" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>94039100</v>
       </c>
@@ -10028,8 +10494,11 @@
       <c r="T153" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U153" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="154" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>94039100</v>
       </c>
@@ -10090,8 +10559,11 @@
       <c r="T154" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U154" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="155" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>94039100</v>
       </c>
@@ -10152,8 +10624,11 @@
       <c r="T155" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U155" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="156" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>94039100</v>
       </c>
@@ -10214,8 +10689,11 @@
       <c r="T156" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U156" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="157" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>94039100</v>
       </c>
@@ -10276,8 +10754,11 @@
       <c r="T157" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U157" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="158" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>94039100</v>
       </c>
@@ -10338,8 +10819,11 @@
       <c r="T158" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U158" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="159" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>94039100</v>
       </c>
@@ -10400,8 +10884,11 @@
       <c r="T159" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U159" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="160" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>94039100</v>
       </c>
@@ -10462,8 +10949,11 @@
       <c r="T160" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U160" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="161" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>94039100</v>
       </c>
@@ -10524,8 +11014,11 @@
       <c r="T161" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U161" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="162" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>94039100</v>
       </c>
@@ -10586,9 +11079,12 @@
       <c r="T162" s="2">
         <v>0</v>
       </c>
+      <c r="U162" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T152" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}"/>
+  <autoFilter ref="A1:U162" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/conf_fiscais.xlsx
+++ b/conf_fiscais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Faturamento\Desktop\nfe_sistema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20FA648-35C4-4016-B097-380385B2423C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B413571-3E7A-4798-91AF-6E82BD675F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F76E099-F64F-4C5B-B230-95152170BA2F}"/>
   </bookViews>
@@ -528,6 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:U162"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -618,7 +619,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>84211210</v>
       </c>
@@ -683,7 +684,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>84502090</v>
       </c>
@@ -748,7 +749,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>84501900</v>
       </c>
@@ -813,7 +814,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>73211100</v>
       </c>
@@ -878,7 +879,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>94016100</v>
       </c>
@@ -943,7 +944,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>94016100</v>
       </c>
@@ -1008,7 +1009,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>94016100</v>
       </c>
@@ -1073,7 +1074,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>94016100</v>
       </c>
@@ -1138,7 +1139,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>94016100</v>
       </c>
@@ -1203,7 +1204,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>94016100</v>
       </c>
@@ -1268,7 +1269,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>84502020</v>
       </c>
@@ -1333,7 +1334,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>84146000</v>
       </c>
@@ -1398,7 +1399,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>84145990</v>
       </c>
@@ -1463,7 +1464,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>84145990</v>
       </c>
@@ -1528,7 +1529,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>84145990</v>
       </c>
@@ -1593,7 +1594,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>84145990</v>
       </c>
@@ -1658,7 +1659,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>84145990</v>
       </c>
@@ -1723,7 +1724,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>84145110</v>
       </c>
@@ -1788,7 +1789,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>84145110</v>
       </c>
@@ -1853,7 +1854,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>84145110</v>
       </c>
@@ -1918,7 +1919,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>94034000</v>
       </c>
@@ -1983,7 +1984,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>94035000</v>
       </c>
@@ -2048,7 +2049,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>94036000</v>
       </c>
@@ -2113,7 +2114,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>73211100</v>
       </c>
@@ -2178,7 +2179,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>84146000</v>
       </c>
@@ -2243,7 +2244,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>84211210</v>
       </c>
@@ -2308,7 +2309,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>84501900</v>
       </c>
@@ -2373,7 +2374,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>84502020</v>
       </c>
@@ -2438,7 +2439,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>84502090</v>
       </c>
@@ -2503,7 +2504,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>94034000</v>
       </c>
@@ -2568,7 +2569,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>94035000</v>
       </c>
@@ -2633,7 +2634,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>94036000</v>
       </c>
@@ -2698,7 +2699,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>94044000</v>
       </c>
@@ -2763,7 +2764,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>94044000</v>
       </c>
@@ -2828,7 +2829,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>94044000</v>
       </c>
@@ -2893,7 +2894,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>94044000</v>
       </c>
@@ -2958,7 +2959,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>94044000</v>
       </c>
@@ -3023,7 +3024,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>94044000</v>
       </c>
@@ -3088,7 +3089,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>94044000</v>
       </c>
@@ -3153,7 +3154,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>94044000</v>
       </c>
@@ -3218,7 +3219,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>94032010</v>
       </c>
@@ -3283,7 +3284,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>94032010</v>
       </c>
@@ -3348,7 +3349,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>94032010</v>
       </c>
@@ -3413,7 +3414,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>94032010</v>
       </c>
@@ -3478,7 +3479,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>94032010</v>
       </c>
@@ -3543,7 +3544,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>94032010</v>
       </c>
@@ -3608,7 +3609,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>94049000</v>
       </c>
@@ -3673,7 +3674,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>94049000</v>
       </c>
@@ -3738,7 +3739,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>94049000</v>
       </c>
@@ -3803,7 +3804,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>94049000</v>
       </c>
@@ -3868,7 +3869,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>94049000</v>
       </c>
@@ -3933,7 +3934,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>94049000</v>
       </c>
@@ -3998,7 +3999,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>85167910</v>
       </c>
@@ -4063,7 +4064,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>85167920</v>
       </c>
@@ -4128,7 +4129,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>85094010</v>
       </c>
@@ -4193,7 +4194,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>85094050</v>
       </c>
@@ -4258,7 +4259,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>85167910</v>
       </c>
@@ -4323,7 +4324,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>85167920</v>
       </c>
@@ -4388,7 +4389,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>85094010</v>
       </c>
@@ -4453,7 +4454,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>85094050</v>
       </c>
@@ -4518,7 +4519,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>85167910</v>
       </c>
@@ -4583,7 +4584,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>85167920</v>
       </c>
@@ -4648,7 +4649,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>85094010</v>
       </c>
@@ -4713,7 +4714,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>85094050</v>
       </c>
@@ -4778,7 +4779,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>85167910</v>
       </c>
@@ -4843,7 +4844,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>85167920</v>
       </c>
@@ -4908,7 +4909,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>85094010</v>
       </c>
@@ -4973,7 +4974,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>85094050</v>
       </c>
@@ -5038,7 +5039,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>85167910</v>
       </c>
@@ -5103,7 +5104,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>85167920</v>
       </c>
@@ -5168,7 +5169,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>85094010</v>
       </c>
@@ -5233,7 +5234,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>85094050</v>
       </c>
@@ -5298,7 +5299,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>85167910</v>
       </c>
@@ -5363,7 +5364,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>85167920</v>
       </c>
@@ -5428,7 +5429,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>85094010</v>
       </c>
@@ -5493,7 +5494,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>85094050</v>
       </c>
@@ -5558,7 +5559,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>85167910</v>
       </c>
@@ -5623,7 +5624,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>85167920</v>
       </c>
@@ -5688,7 +5689,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>85094010</v>
       </c>
@@ -5753,7 +5754,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>85094050</v>
       </c>
@@ -5818,7 +5819,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>85167910</v>
       </c>
@@ -5883,7 +5884,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>85167920</v>
       </c>
@@ -5948,7 +5949,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>85094010</v>
       </c>
@@ -6013,7 +6014,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>85094050</v>
       </c>
@@ -6078,7 +6079,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>84186931</v>
       </c>
@@ -6143,7 +6144,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>84186931</v>
       </c>
@@ -6208,7 +6209,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>84186931</v>
       </c>
@@ -6273,7 +6274,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>84186931</v>
       </c>
@@ -6338,7 +6339,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>84186931</v>
       </c>
@@ -6403,7 +6404,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>84186931</v>
       </c>
@@ -6468,7 +6469,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>84186931</v>
       </c>
@@ -6533,7 +6534,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>84186931</v>
       </c>
@@ -6598,7 +6599,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>84145190</v>
       </c>
@@ -6663,7 +6664,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>84145190</v>
       </c>
@@ -6728,7 +6729,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>84145190</v>
       </c>
@@ -6793,7 +6794,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>84145190</v>
       </c>
@@ -6858,7 +6859,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>84145190</v>
       </c>
@@ -6923,7 +6924,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>84145190</v>
       </c>
@@ -6988,7 +6989,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>84145190</v>
       </c>
@@ -7053,7 +7054,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>84145190</v>
       </c>
@@ -7118,7 +7119,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>84145190</v>
       </c>
@@ -7183,7 +7184,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>84145190</v>
       </c>
@@ -7248,7 +7249,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>84145190</v>
       </c>
@@ -7313,7 +7314,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>84145190</v>
       </c>
@@ -7378,7 +7379,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>73211100</v>
       </c>
@@ -7443,7 +7444,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>84211210</v>
       </c>
@@ -7508,7 +7509,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>94042900</v>
       </c>
@@ -7573,7 +7574,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>94042900</v>
       </c>
@@ -7638,7 +7639,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>94042900</v>
       </c>
@@ -7703,7 +7704,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>94042900</v>
       </c>
@@ -7768,7 +7769,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>94042900</v>
       </c>
@@ -7833,7 +7834,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>94042900</v>
       </c>
@@ -7898,7 +7899,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>94042900</v>
       </c>
@@ -7963,7 +7964,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>94042900</v>
       </c>
@@ -8028,7 +8029,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>94041000</v>
       </c>
@@ -8093,7 +8094,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>94041000</v>
       </c>
@@ -8158,7 +8159,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>94041000</v>
       </c>
@@ -8223,7 +8224,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>94041000</v>
       </c>
@@ -8288,7 +8289,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>94041000</v>
       </c>
@@ -8353,7 +8354,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>94041000</v>
       </c>
@@ -8418,7 +8419,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>94041000</v>
       </c>
@@ -8483,7 +8484,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>94041000</v>
       </c>
@@ -8548,7 +8549,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>94035000</v>
       </c>
@@ -8613,7 +8614,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>94035000</v>
       </c>
@@ -8678,7 +8679,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>94035000</v>
       </c>
@@ -8743,7 +8744,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>94035000</v>
       </c>
@@ -8808,7 +8809,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>94035000</v>
       </c>
@@ -8873,7 +8874,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>94035000</v>
       </c>
@@ -8938,7 +8939,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>94034000</v>
       </c>
@@ -9003,7 +9004,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>94034000</v>
       </c>
@@ -9068,7 +9069,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>94034000</v>
       </c>
@@ -9133,7 +9134,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>94034000</v>
       </c>
@@ -9198,7 +9199,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>94034000</v>
       </c>
@@ -9263,7 +9264,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>94034000</v>
       </c>
@@ -9328,7 +9329,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>94036000</v>
       </c>
@@ -9393,7 +9394,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>94036000</v>
       </c>
@@ -9458,7 +9459,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>94036000</v>
       </c>
@@ -9523,7 +9524,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>94036000</v>
       </c>
@@ -9588,7 +9589,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>94036000</v>
       </c>
@@ -9653,7 +9654,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>94036000</v>
       </c>
@@ -9718,7 +9719,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>73211100</v>
       </c>
@@ -9783,7 +9784,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>73211100</v>
       </c>
@@ -9848,7 +9849,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>84501900</v>
       </c>
@@ -9913,7 +9914,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>84501900</v>
       </c>
@@ -9978,7 +9979,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>84501900</v>
       </c>
@@ -10043,7 +10044,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>84501900</v>
       </c>
@@ -10108,7 +10109,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>84501900</v>
       </c>
@@ -10173,7 +10174,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>84501900</v>
       </c>
@@ -10238,7 +10239,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>84502020</v>
       </c>
@@ -10320,10 +10321,10 @@
         <v>6108</v>
       </c>
       <c r="F151" s="2">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G151" s="2">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H151" s="2">
         <v>0</v>
@@ -10385,10 +10386,10 @@
         <v>6108</v>
       </c>
       <c r="F152" s="2">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G152" s="2">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H152" s="2">
         <v>0</v>
@@ -10450,10 +10451,10 @@
         <v>5102</v>
       </c>
       <c r="F153" s="2">
-        <v>0</v>
+        <v>5102</v>
       </c>
       <c r="G153" s="2">
-        <v>5102</v>
+        <v>0</v>
       </c>
       <c r="H153" s="2">
         <v>0</v>
@@ -10515,10 +10516,10 @@
         <v>6108</v>
       </c>
       <c r="F154" s="2">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G154" s="2">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H154" s="2">
         <v>0</v>
@@ -10580,10 +10581,10 @@
         <v>6108</v>
       </c>
       <c r="F155" s="2">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G155" s="2">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H155" s="2">
         <v>0</v>
@@ -10645,10 +10646,10 @@
         <v>6108</v>
       </c>
       <c r="F156" s="2">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G156" s="2">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H156" s="2">
         <v>0</v>
@@ -10710,10 +10711,10 @@
         <v>6108</v>
       </c>
       <c r="F157" s="2">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G157" s="2">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H157" s="2">
         <v>0</v>
@@ -10775,10 +10776,10 @@
         <v>6108</v>
       </c>
       <c r="F158" s="2">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G158" s="2">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H158" s="2">
         <v>0</v>
@@ -10840,10 +10841,10 @@
         <v>6108</v>
       </c>
       <c r="F159" s="2">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G159" s="2">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H159" s="2">
         <v>0</v>
@@ -10905,10 +10906,10 @@
         <v>6108</v>
       </c>
       <c r="F160" s="2">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G160" s="2">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H160" s="2">
         <v>0</v>
@@ -10970,10 +10971,10 @@
         <v>6108</v>
       </c>
       <c r="F161" s="2">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G161" s="2">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H161" s="2">
         <v>0</v>
@@ -11035,10 +11036,10 @@
         <v>5102</v>
       </c>
       <c r="F162" s="2">
-        <v>0</v>
+        <v>5102</v>
       </c>
       <c r="G162" s="2">
-        <v>5102</v>
+        <v>0</v>
       </c>
       <c r="H162" s="2">
         <v>0</v>
@@ -11084,7 +11085,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U162" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}"/>
+  <autoFilter ref="A1:U162" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="94039100"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/conf_fiscais.xlsx
+++ b/conf_fiscais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Faturamento\Desktop\nfe_sistema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F198C1-CD93-424F-9ECC-9F0AA9313083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1A0C98-FE82-4CD3-86C9-54656960264D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="492" yWindow="324" windowWidth="13596" windowHeight="11616" activeTab="2" xr2:uid="{6F76E099-F64F-4C5B-B230-95152170BA2F}"/>
   </bookViews>

--- a/conf_fiscais.xlsx
+++ b/conf_fiscais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Faturamento\Desktop\nfe_sistema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1A0C98-FE82-4CD3-86C9-54656960264D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CD9000-6BB1-4574-8AE6-95F0CA86147D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="492" yWindow="324" windowWidth="13596" windowHeight="11616" activeTab="2" xr2:uid="{6F76E099-F64F-4C5B-B230-95152170BA2F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{6F76E099-F64F-4C5B-B230-95152170BA2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Config Fiscal" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2650" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2668" uniqueCount="58">
   <si>
     <t>ncm</t>
   </si>
@@ -182,12 +182,37 @@
   <si>
     <t>Venda por conta e ordem</t>
   </si>
+  <si>
+    <t>Uso e Consumo</t>
+  </si>
+  <si>
+    <t>Compra de material de uso ou consumo de fornecedor em outro estado</t>
+  </si>
+  <si>
+    <t>Compra de material de uso ou consumo dentro do mesmo estado</t>
+  </si>
+  <si>
+    <t>Devolução de venda de produção do estabelecimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+Devolução de venda de mercadoria adquirida ou recebida de terceiros</t>
+  </si>
+  <si>
+    <t>Entrada Fornecedor</t>
+  </si>
+  <si>
+    <t>Venda de combustível</t>
+  </si>
+  <si>
+    <t>Combustível entrega</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,6 +252,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -270,7 +302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -296,6 +328,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -79527,13 +79571,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C8E52B2-7C9A-44A3-BDF7-2311E94722D5}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
@@ -79831,7 +79875,134 @@
         <v>49</v>
       </c>
     </row>
+    <row r="22" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
+        <v>5101</v>
+      </c>
+      <c r="B22" s="4">
+        <v>1556</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
+        <v>6101</v>
+      </c>
+      <c r="B23" s="4">
+        <v>2556</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
+        <v>5102</v>
+      </c>
+      <c r="B24" s="4">
+        <v>1556</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
+        <v>6102</v>
+      </c>
+      <c r="B25" s="4">
+        <v>2556</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
+        <v>1201</v>
+      </c>
+      <c r="B26" s="11">
+        <v>1201</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
+        <v>2201</v>
+      </c>
+      <c r="B27" s="11">
+        <v>2201</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
+        <v>1202</v>
+      </c>
+      <c r="B28" s="11">
+        <v>1202</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="5">
+        <v>2202</v>
+      </c>
+      <c r="B29" s="11">
+        <v>2202</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" s="12" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="12">
+        <v>5656</v>
+      </c>
+      <c r="B30" s="12">
+        <v>1653</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>